--- a/Specifications/Nonresidential/v2.0/RetailMedium_Prototype_Scorecard.xlsx
+++ b/Specifications/Nonresidential/v2.0/RetailMedium_Prototype_Scorecard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cursor\Check dictation and Spelling\Clean-uploaded to GH-6Oct2026\Without Weights\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\src\NOR-Codes-Stds\CalBEM-Prototypes\Specifications\Nonresidential\v2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B45F3B-CA66-4A2B-B70F-AB2D4DE6FF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A39444A-25F3-4891-8AF0-7EAED5C98904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="890" firstSheet="1" activeTab="1" xr2:uid="{EAC23EE3-0CA0-4FF8-990D-9B21A59FA3E0}"/>
   </bookViews>
@@ -1481,6 +1481,7 @@
         <sz val="12"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Efficiency of HVAC System
 </t>
@@ -1490,6 +1491,7 @@
         <sz val="10"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> (Efficiency is capacity-dependent. The following table provides a general estimate of system efficiency based on preliminary simulations in one climate zone, or assuming cooling load based on rule of thumb)</t>
     </r>
@@ -2690,7 +2692,7 @@
     <numFmt numFmtId="169" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="170" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="68" x14ac:knownFonts="1">
+  <fonts count="67" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3074,13 +3076,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3117,12 +3112,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Arial"/>
@@ -3132,17 +3121,26 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="55">
@@ -3455,7 +3453,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="208">
+  <borders count="213">
     <border>
       <left/>
       <right/>
@@ -6134,6 +6132,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -6192,9 +6251,9 @@
     <xf numFmtId="0" fontId="11" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="795">
+  <cellXfs count="798">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6976,17 +7035,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="56"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="56"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="56" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="56" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="56" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="112" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6999,7 +7058,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7011,7 +7070,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="5" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -7246,7 +7305,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="64" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7265,7 +7324,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7854,17 +7913,17 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -7872,28 +7931,79 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="9" borderId="133" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="9" borderId="128" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="9" borderId="134" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7902,123 +8012,48 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="138" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="141" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="9" borderId="156" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="64" fillId="9" borderId="143" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="9" borderId="133" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="9" borderId="128" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="9" borderId="134" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="9" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="9" borderId="125" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="9" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="54" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="9" borderId="156" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="9" borderId="143" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="203" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8127,6 +8162,330 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="193" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="196" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="194" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="146" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="185" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="187" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="207" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="188" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="175" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="176" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="171" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -8136,333 +8495,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="160" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="163" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="161" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="164" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="165" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="166" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="171" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="167" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="172" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="188" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="175" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="176" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="193" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="196" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="204" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="194" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="197" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="205" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="181" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="206" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="146" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="178" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="185" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="187" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="190" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="207" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -8495,6 +8530,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="209" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="210" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="211" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="208" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="212" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="159" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="117" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="125" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="57">
@@ -17854,11 +17922,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="584" t="s">
+      <c r="A1" s="581" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="584"/>
-      <c r="C1" s="584"/>
+      <c r="B1" s="581"/>
+      <c r="C1" s="581"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="582" t="s">
@@ -17951,7 +18019,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A10" s="583" t="s">
+      <c r="A10" s="584" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="585" t="s">
@@ -17965,7 +18033,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="583"/>
+      <c r="A11" s="584"/>
       <c r="B11" s="585"/>
       <c r="C11" s="300" t="s">
         <v>20</v>
@@ -17975,7 +18043,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="583"/>
+      <c r="A12" s="584"/>
       <c r="B12" s="387" t="s">
         <v>22</v>
       </c>
@@ -17987,7 +18055,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="583"/>
+      <c r="A13" s="584"/>
       <c r="B13" s="295" t="s">
         <v>24</v>
       </c>
@@ -17999,7 +18067,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="583"/>
+      <c r="A14" s="584"/>
       <c r="B14" s="387" t="s">
         <v>26</v>
       </c>
@@ -18011,7 +18079,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="583"/>
+      <c r="A15" s="584"/>
       <c r="C15" s="557"/>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -18194,11 +18262,11 @@
       <c r="C32" s="557"/>
     </row>
     <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A33" s="584" t="s">
+      <c r="A33" s="581" t="s">
         <v>54</v>
       </c>
-      <c r="B33" s="584"/>
-      <c r="C33" s="584"/>
+      <c r="B33" s="581"/>
+      <c r="C33" s="581"/>
     </row>
     <row r="34" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C34" s="557"/>
@@ -18245,11 +18313,11 @@
       <c r="C46" s="557"/>
     </row>
     <row r="47" spans="1:8" ht="67.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="584" t="s">
+      <c r="A47" s="581" t="s">
         <v>56</v>
       </c>
-      <c r="B47" s="584"/>
-      <c r="C47" s="584"/>
+      <c r="B47" s="581"/>
+      <c r="C47" s="581"/>
       <c r="E47" s="549"/>
       <c r="F47" s="547"/>
       <c r="G47" s="547"/>
@@ -18267,18 +18335,18 @@
       <c r="H48" s="547"/>
     </row>
     <row r="49" spans="1:8" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="581"/>
-      <c r="B49" s="581"/>
-      <c r="C49" s="581"/>
+      <c r="A49" s="583"/>
+      <c r="B49" s="583"/>
+      <c r="C49" s="583"/>
       <c r="E49" s="549"/>
       <c r="F49" s="547"/>
       <c r="G49" s="547"/>
       <c r="H49" s="547"/>
     </row>
     <row r="50" spans="1:8" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="581"/>
-      <c r="B50" s="581"/>
-      <c r="C50" s="581"/>
+      <c r="A50" s="583"/>
+      <c r="B50" s="583"/>
+      <c r="C50" s="583"/>
       <c r="E50" s="549"/>
       <c r="F50" s="547"/>
       <c r="G50" s="547"/>
@@ -18348,13 +18416,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="667" t="str">
+      <c r="A1" s="659" t="str">
         <f>"Exterior Lighting - "&amp;Prototype!A2</f>
         <v>Exterior Lighting - RetailMedium</v>
       </c>
-      <c r="B1" s="667"/>
-      <c r="C1" s="667"/>
-      <c r="D1" s="667"/>
+      <c r="B1" s="659"/>
+      <c r="C1" s="659"/>
+      <c r="D1" s="659"/>
     </row>
     <row r="2" spans="1:11" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
@@ -18398,24 +18466,24 @@
       <c r="C5" s="387"/>
     </row>
     <row r="6" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="667" t="s">
+      <c r="A6" s="659" t="s">
         <v>487</v>
       </c>
-      <c r="B6" s="667"/>
-      <c r="C6" s="667"/>
-      <c r="D6" s="667"/>
-      <c r="E6" s="667"/>
-      <c r="F6" s="667"/>
-      <c r="G6" s="667"/>
+      <c r="B6" s="659"/>
+      <c r="C6" s="659"/>
+      <c r="D6" s="659"/>
+      <c r="E6" s="659"/>
+      <c r="F6" s="659"/>
+      <c r="G6" s="659"/>
     </row>
     <row r="7" spans="1:11" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A7" s="69" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="669" t="s">
+      <c r="B7" s="661" t="s">
         <v>489</v>
       </c>
-      <c r="C7" s="670"/>
+      <c r="C7" s="662"/>
       <c r="D7" s="111" t="s">
         <v>490</v>
       </c>
@@ -18579,42 +18647,42 @@
       <c r="K13" s="199"/>
     </row>
     <row r="14" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="668" t="s">
+      <c r="A14" s="660" t="s">
         <v>510</v>
       </c>
-      <c r="B14" s="668"/>
-      <c r="C14" s="668"/>
-      <c r="D14" s="668"/>
-      <c r="E14" s="668"/>
-      <c r="F14" s="668"/>
+      <c r="B14" s="660"/>
+      <c r="C14" s="660"/>
+      <c r="D14" s="660"/>
+      <c r="E14" s="660"/>
+      <c r="F14" s="660"/>
       <c r="G14" s="112">
         <f>SUM(G8:G13)-G15</f>
         <v>796.27555555555546</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="668" t="s">
+      <c r="A15" s="660" t="s">
         <v>511</v>
       </c>
-      <c r="B15" s="668"/>
-      <c r="C15" s="668"/>
-      <c r="D15" s="668"/>
-      <c r="E15" s="668"/>
-      <c r="F15" s="668"/>
+      <c r="B15" s="660"/>
+      <c r="C15" s="660"/>
+      <c r="D15" s="660"/>
+      <c r="E15" s="660"/>
+      <c r="F15" s="660"/>
       <c r="G15" s="112">
         <f>G11+G12</f>
         <v>651.28440000000001</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="668" t="s">
+      <c r="A16" s="660" t="s">
         <v>163</v>
       </c>
-      <c r="B16" s="668"/>
-      <c r="C16" s="668"/>
-      <c r="D16" s="668"/>
-      <c r="E16" s="668"/>
-      <c r="F16" s="668"/>
+      <c r="B16" s="660"/>
+      <c r="C16" s="660"/>
+      <c r="D16" s="660"/>
+      <c r="E16" s="660"/>
+      <c r="F16" s="660"/>
       <c r="G16" s="112">
         <f t="shared" ref="G16" si="0">G14+G15</f>
         <v>1447.5599555555555</v>
@@ -18738,15 +18806,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="671" t="str">
+      <c r="A1" s="663" t="str">
         <f>"Equipment - "&amp;Prototype!A2</f>
         <v>Equipment - RetailMedium</v>
       </c>
-      <c r="B1" s="667"/>
-      <c r="C1" s="667"/>
-      <c r="D1" s="667"/>
-      <c r="E1" s="667"/>
-      <c r="F1" s="667"/>
+      <c r="B1" s="659"/>
+      <c r="C1" s="659"/>
+      <c r="D1" s="659"/>
+      <c r="E1" s="659"/>
+      <c r="F1" s="659"/>
     </row>
     <row r="2" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="179" t="s">
@@ -19016,38 +19084,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="626" t="str">
+      <c r="A1" s="622" t="str">
         <f>"Schedules - "&amp;Prototype!A2</f>
         <v>Schedules - RetailMedium</v>
       </c>
-      <c r="B1" s="626"/>
-      <c r="C1" s="626"/>
-      <c r="D1" s="626"/>
-      <c r="E1" s="626"/>
-      <c r="F1" s="626"/>
-      <c r="G1" s="626"/>
-      <c r="H1" s="626"/>
-      <c r="I1" s="626"/>
-      <c r="J1" s="626"/>
-      <c r="K1" s="626"/>
-      <c r="L1" s="626"/>
-      <c r="M1" s="626"/>
-      <c r="N1" s="626"/>
-      <c r="O1" s="626"/>
-      <c r="P1" s="626"/>
-      <c r="Q1" s="626"/>
-      <c r="R1" s="626"/>
-      <c r="S1" s="626"/>
-      <c r="T1" s="626"/>
-      <c r="U1" s="626"/>
-      <c r="V1" s="626"/>
-      <c r="W1" s="626"/>
-      <c r="X1" s="626"/>
-      <c r="Y1" s="626"/>
-      <c r="Z1" s="626"/>
-      <c r="AA1" s="626"/>
-      <c r="AB1" s="626"/>
-      <c r="AC1" s="708"/>
+      <c r="B1" s="622"/>
+      <c r="C1" s="622"/>
+      <c r="D1" s="622"/>
+      <c r="E1" s="622"/>
+      <c r="F1" s="622"/>
+      <c r="G1" s="622"/>
+      <c r="H1" s="622"/>
+      <c r="I1" s="622"/>
+      <c r="J1" s="622"/>
+      <c r="K1" s="622"/>
+      <c r="L1" s="622"/>
+      <c r="M1" s="622"/>
+      <c r="N1" s="622"/>
+      <c r="O1" s="622"/>
+      <c r="P1" s="622"/>
+      <c r="Q1" s="622"/>
+      <c r="R1" s="622"/>
+      <c r="S1" s="622"/>
+      <c r="T1" s="622"/>
+      <c r="U1" s="622"/>
+      <c r="V1" s="622"/>
+      <c r="W1" s="622"/>
+      <c r="X1" s="622"/>
+      <c r="Y1" s="622"/>
+      <c r="Z1" s="622"/>
+      <c r="AA1" s="622"/>
+      <c r="AB1" s="622"/>
+      <c r="AC1" s="744"/>
       <c r="AD1" s="37"/>
       <c r="AE1" s="37"/>
       <c r="AF1" s="37"/>
@@ -19058,47 +19126,47 @@
       <c r="AK1" s="38"/>
     </row>
     <row r="2" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="661" t="s">
+      <c r="A2" s="653" t="s">
         <v>533</v>
       </c>
-      <c r="B2" s="661" t="s">
+      <c r="B2" s="653" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="661" t="s">
+      <c r="C2" s="653" t="s">
         <v>534</v>
       </c>
-      <c r="D2" s="661" t="s">
+      <c r="D2" s="653" t="s">
         <v>259</v>
       </c>
-      <c r="E2" s="661" t="s">
+      <c r="E2" s="653" t="s">
         <v>535</v>
       </c>
-      <c r="F2" s="724" t="s">
+      <c r="F2" s="760" t="s">
         <v>536</v>
       </c>
-      <c r="G2" s="724"/>
-      <c r="H2" s="724"/>
-      <c r="I2" s="724"/>
-      <c r="J2" s="724"/>
-      <c r="K2" s="724"/>
-      <c r="L2" s="724"/>
-      <c r="M2" s="724"/>
-      <c r="N2" s="724"/>
-      <c r="O2" s="724"/>
-      <c r="P2" s="724"/>
-      <c r="Q2" s="724"/>
-      <c r="R2" s="724"/>
-      <c r="S2" s="724"/>
-      <c r="T2" s="724"/>
-      <c r="U2" s="724"/>
-      <c r="V2" s="724"/>
-      <c r="W2" s="724"/>
-      <c r="X2" s="724"/>
-      <c r="Y2" s="724"/>
-      <c r="Z2" s="724"/>
-      <c r="AA2" s="724"/>
-      <c r="AB2" s="724"/>
-      <c r="AC2" s="724"/>
+      <c r="G2" s="760"/>
+      <c r="H2" s="760"/>
+      <c r="I2" s="760"/>
+      <c r="J2" s="760"/>
+      <c r="K2" s="760"/>
+      <c r="L2" s="760"/>
+      <c r="M2" s="760"/>
+      <c r="N2" s="760"/>
+      <c r="O2" s="760"/>
+      <c r="P2" s="760"/>
+      <c r="Q2" s="760"/>
+      <c r="R2" s="760"/>
+      <c r="S2" s="760"/>
+      <c r="T2" s="760"/>
+      <c r="U2" s="760"/>
+      <c r="V2" s="760"/>
+      <c r="W2" s="760"/>
+      <c r="X2" s="760"/>
+      <c r="Y2" s="760"/>
+      <c r="Z2" s="760"/>
+      <c r="AA2" s="760"/>
+      <c r="AB2" s="760"/>
+      <c r="AC2" s="760"/>
       <c r="AD2" s="37"/>
       <c r="AE2" s="37"/>
       <c r="AF2" s="37"/>
@@ -19109,11 +19177,11 @@
       <c r="AK2" s="38"/>
     </row>
     <row r="3" spans="1:39" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="662"/>
-      <c r="B3" s="662"/>
-      <c r="C3" s="662"/>
-      <c r="D3" s="662"/>
-      <c r="E3" s="662"/>
+      <c r="A3" s="654"/>
+      <c r="B3" s="654"/>
+      <c r="C3" s="654"/>
+      <c r="D3" s="654"/>
+      <c r="E3" s="654"/>
       <c r="F3" s="567">
         <v>1</v>
       </c>
@@ -19196,16 +19264,16 @@
       <c r="AK3" s="38"/>
     </row>
     <row r="4" spans="1:39" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="709" t="s">
+      <c r="A4" s="745" t="s">
         <v>537</v>
       </c>
-      <c r="B4" s="712" t="s">
+      <c r="B4" s="749" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="723" t="s">
+      <c r="C4" s="758" t="s">
         <v>538</v>
       </c>
-      <c r="D4" s="720" t="s">
+      <c r="D4" s="688" t="s">
         <v>539</v>
       </c>
       <c r="E4" s="210" t="s">
@@ -19293,10 +19361,10 @@
       <c r="AK4" s="38"/>
     </row>
     <row r="5" spans="1:39" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="710"/>
-      <c r="B5" s="685"/>
-      <c r="C5" s="685"/>
-      <c r="D5" s="721"/>
+      <c r="A5" s="746"/>
+      <c r="B5" s="750"/>
+      <c r="C5" s="750"/>
+      <c r="D5" s="689"/>
       <c r="E5" s="208" t="s">
         <v>541</v>
       </c>
@@ -19382,10 +19450,10 @@
       <c r="AK5" s="38"/>
     </row>
     <row r="6" spans="1:39" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="711"/>
-      <c r="B6" s="713"/>
-      <c r="C6" s="713"/>
-      <c r="D6" s="722"/>
+      <c r="A6" s="747"/>
+      <c r="B6" s="751"/>
+      <c r="C6" s="751"/>
+      <c r="D6" s="690"/>
       <c r="E6" s="212" t="s">
         <v>542</v>
       </c>
@@ -19471,18 +19539,18 @@
       <c r="AK6" s="38"/>
     </row>
     <row r="7" spans="1:39" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="681" t="str">
+      <c r="A7" s="748" t="str">
         <f>A4</f>
         <v>All Zones</v>
       </c>
-      <c r="B7" s="714" t="str">
+      <c r="B7" s="752" t="str">
         <f>B4</f>
         <v>Retail</v>
       </c>
-      <c r="C7" s="684" t="s">
+      <c r="C7" s="756" t="s">
         <v>543</v>
       </c>
-      <c r="D7" s="696" t="s">
+      <c r="D7" s="759" t="s">
         <v>544</v>
       </c>
       <c r="E7" s="207" t="s">
@@ -19570,10 +19638,10 @@
       <c r="AK7" s="38"/>
     </row>
     <row r="8" spans="1:39" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="682"/>
-      <c r="B8" s="692"/>
-      <c r="C8" s="685"/>
-      <c r="D8" s="697"/>
+      <c r="A8" s="718"/>
+      <c r="B8" s="721"/>
+      <c r="C8" s="750"/>
+      <c r="D8" s="727"/>
       <c r="E8" s="109" t="s">
         <v>541</v>
       </c>
@@ -19659,10 +19727,10 @@
       <c r="AK8" s="38"/>
     </row>
     <row r="9" spans="1:39" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="683"/>
-      <c r="B9" s="715"/>
-      <c r="C9" s="686"/>
-      <c r="D9" s="698"/>
+      <c r="A9" s="737"/>
+      <c r="B9" s="738"/>
+      <c r="C9" s="757"/>
+      <c r="D9" s="732"/>
       <c r="E9" s="137" t="s">
         <v>542</v>
       </c>
@@ -19748,18 +19816,18 @@
       <c r="AK9" s="38"/>
     </row>
     <row r="10" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="689" t="str">
+      <c r="A10" s="717" t="str">
         <f>A4</f>
         <v>All Zones</v>
       </c>
-      <c r="B10" s="691" t="str">
+      <c r="B10" s="720" t="str">
         <f>B4</f>
         <v>Retail</v>
       </c>
-      <c r="C10" s="719" t="s">
+      <c r="C10" s="729" t="s">
         <v>545</v>
       </c>
-      <c r="D10" s="716" t="s">
+      <c r="D10" s="753" t="s">
         <v>546</v>
       </c>
       <c r="E10" s="140" t="s">
@@ -19848,10 +19916,10 @@
       <c r="AM10" s="49"/>
     </row>
     <row r="11" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="682"/>
-      <c r="B11" s="692"/>
-      <c r="C11" s="694"/>
-      <c r="D11" s="717"/>
+      <c r="A11" s="718"/>
+      <c r="B11" s="721"/>
+      <c r="C11" s="730"/>
+      <c r="D11" s="754"/>
       <c r="E11" s="109" t="s">
         <v>541</v>
       </c>
@@ -19938,10 +20006,10 @@
       <c r="AM11" s="49"/>
     </row>
     <row r="12" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="690"/>
-      <c r="B12" s="693"/>
-      <c r="C12" s="695"/>
-      <c r="D12" s="718"/>
+      <c r="A12" s="719"/>
+      <c r="B12" s="722"/>
+      <c r="C12" s="740"/>
+      <c r="D12" s="755"/>
       <c r="E12" s="137" t="s">
         <v>542</v>
       </c>
@@ -20028,18 +20096,18 @@
       <c r="AM12" s="49"/>
     </row>
     <row r="13" spans="1:39" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="689" t="str">
+      <c r="A13" s="717" t="str">
         <f t="shared" ref="A13:B13" si="0">A7</f>
         <v>All Zones</v>
       </c>
-      <c r="B13" s="691" t="str">
+      <c r="B13" s="720" t="str">
         <f t="shared" si="0"/>
         <v>Retail</v>
       </c>
-      <c r="C13" s="719" t="s">
+      <c r="C13" s="729" t="s">
         <v>547</v>
       </c>
-      <c r="D13" s="752" t="s">
+      <c r="D13" s="726" t="s">
         <v>544</v>
       </c>
       <c r="E13" s="146" t="s">
@@ -20119,10 +20187,10 @@
       </c>
     </row>
     <row r="14" spans="1:39" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="682"/>
-      <c r="B14" s="692"/>
-      <c r="C14" s="694"/>
-      <c r="D14" s="697"/>
+      <c r="A14" s="718"/>
+      <c r="B14" s="721"/>
+      <c r="C14" s="730"/>
+      <c r="D14" s="727"/>
       <c r="E14" s="149" t="s">
         <v>541</v>
       </c>
@@ -20200,10 +20268,10 @@
       </c>
     </row>
     <row r="15" spans="1:39" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="690"/>
-      <c r="B15" s="693"/>
-      <c r="C15" s="754"/>
-      <c r="D15" s="698"/>
+      <c r="A15" s="719"/>
+      <c r="B15" s="722"/>
+      <c r="C15" s="731"/>
+      <c r="D15" s="732"/>
       <c r="E15" s="152" t="s">
         <v>542</v>
       </c>
@@ -20281,18 +20349,18 @@
       </c>
     </row>
     <row r="16" spans="1:39" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="689" t="str">
+      <c r="A16" s="717" t="str">
         <f t="shared" ref="A16:B16" si="1">A10</f>
         <v>All Zones</v>
       </c>
-      <c r="B16" s="691" t="str">
+      <c r="B16" s="720" t="str">
         <f t="shared" si="1"/>
         <v>Retail</v>
       </c>
-      <c r="C16" s="750" t="s">
+      <c r="C16" s="724" t="s">
         <v>548</v>
       </c>
-      <c r="D16" s="752" t="s">
+      <c r="D16" s="726" t="s">
         <v>544</v>
       </c>
       <c r="E16" s="146" t="s">
@@ -20372,10 +20440,10 @@
       </c>
     </row>
     <row r="17" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="682"/>
-      <c r="B17" s="692"/>
-      <c r="C17" s="750"/>
-      <c r="D17" s="697"/>
+      <c r="A17" s="718"/>
+      <c r="B17" s="721"/>
+      <c r="C17" s="724"/>
+      <c r="D17" s="727"/>
       <c r="E17" s="149" t="s">
         <v>541</v>
       </c>
@@ -20453,10 +20521,10 @@
       </c>
     </row>
     <row r="18" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="690"/>
-      <c r="B18" s="693"/>
-      <c r="C18" s="750"/>
-      <c r="D18" s="698"/>
+      <c r="A18" s="719"/>
+      <c r="B18" s="722"/>
+      <c r="C18" s="724"/>
+      <c r="D18" s="732"/>
       <c r="E18" s="152" t="s">
         <v>542</v>
       </c>
@@ -20534,18 +20602,18 @@
       </c>
     </row>
     <row r="19" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="689" t="str">
+      <c r="A19" s="717" t="str">
         <f t="shared" ref="A19:B19" si="2">A13</f>
         <v>All Zones</v>
       </c>
-      <c r="B19" s="691" t="str">
+      <c r="B19" s="720" t="str">
         <f t="shared" si="2"/>
         <v>Retail</v>
       </c>
-      <c r="C19" s="749" t="s">
+      <c r="C19" s="723" t="s">
         <v>239</v>
       </c>
-      <c r="D19" s="752" t="s">
+      <c r="D19" s="726" t="s">
         <v>544</v>
       </c>
       <c r="E19" s="146" t="s">
@@ -20625,10 +20693,10 @@
       </c>
     </row>
     <row r="20" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="682"/>
-      <c r="B20" s="692"/>
-      <c r="C20" s="750"/>
-      <c r="D20" s="697"/>
+      <c r="A20" s="718"/>
+      <c r="B20" s="721"/>
+      <c r="C20" s="724"/>
+      <c r="D20" s="727"/>
       <c r="E20" s="149" t="s">
         <v>541</v>
       </c>
@@ -20706,10 +20774,10 @@
       </c>
     </row>
     <row r="21" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="690"/>
-      <c r="B21" s="693"/>
-      <c r="C21" s="751"/>
-      <c r="D21" s="753"/>
+      <c r="A21" s="719"/>
+      <c r="B21" s="722"/>
+      <c r="C21" s="725"/>
+      <c r="D21" s="728"/>
       <c r="E21" s="152" t="s">
         <v>542</v>
       </c>
@@ -20787,18 +20855,18 @@
       </c>
     </row>
     <row r="22" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="689" t="str">
+      <c r="A22" s="717" t="str">
         <f t="shared" ref="A22:B22" si="3">A16</f>
         <v>All Zones</v>
       </c>
-      <c r="B22" s="691" t="str">
+      <c r="B22" s="720" t="str">
         <f t="shared" si="3"/>
         <v>Retail</v>
       </c>
-      <c r="C22" s="687" t="s">
+      <c r="C22" s="761" t="s">
         <v>549</v>
       </c>
-      <c r="D22" s="696" t="s">
+      <c r="D22" s="759" t="s">
         <v>544</v>
       </c>
       <c r="E22" s="146" t="s">
@@ -20902,10 +20970,10 @@
       </c>
     </row>
     <row r="23" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="682"/>
-      <c r="B23" s="692"/>
-      <c r="C23" s="694"/>
-      <c r="D23" s="697"/>
+      <c r="A23" s="718"/>
+      <c r="B23" s="721"/>
+      <c r="C23" s="730"/>
+      <c r="D23" s="727"/>
       <c r="E23" s="149" t="s">
         <v>541</v>
       </c>
@@ -21007,10 +21075,10 @@
       </c>
     </row>
     <row r="24" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="690"/>
-      <c r="B24" s="693"/>
-      <c r="C24" s="695"/>
-      <c r="D24" s="698"/>
+      <c r="A24" s="719"/>
+      <c r="B24" s="722"/>
+      <c r="C24" s="740"/>
+      <c r="D24" s="732"/>
       <c r="E24" s="159" t="s">
         <v>542</v>
       </c>
@@ -21112,18 +21180,18 @@
       </c>
     </row>
     <row r="25" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="689" t="str">
+      <c r="A25" s="717" t="str">
         <f t="shared" ref="A25:B25" si="4">A19</f>
         <v>All Zones</v>
       </c>
-      <c r="B25" s="691" t="str">
+      <c r="B25" s="720" t="str">
         <f t="shared" si="4"/>
         <v>Retail</v>
       </c>
-      <c r="C25" s="675" t="s">
+      <c r="C25" s="739" t="s">
         <v>550</v>
       </c>
-      <c r="D25" s="678" t="s">
+      <c r="D25" s="741" t="s">
         <v>544</v>
       </c>
       <c r="E25" s="160" t="s">
@@ -21227,10 +21295,10 @@
       </c>
     </row>
     <row r="26" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="682"/>
-      <c r="B26" s="692"/>
-      <c r="C26" s="694"/>
-      <c r="D26" s="679"/>
+      <c r="A26" s="718"/>
+      <c r="B26" s="721"/>
+      <c r="C26" s="730"/>
+      <c r="D26" s="742"/>
       <c r="E26" s="163" t="s">
         <v>541</v>
       </c>
@@ -21332,10 +21400,10 @@
       </c>
     </row>
     <row r="27" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="683"/>
-      <c r="B27" s="715"/>
-      <c r="C27" s="695"/>
-      <c r="D27" s="725"/>
+      <c r="A27" s="737"/>
+      <c r="B27" s="738"/>
+      <c r="C27" s="740"/>
+      <c r="D27" s="743"/>
       <c r="E27" s="352" t="s">
         <v>542</v>
       </c>
@@ -21437,49 +21505,49 @@
       </c>
     </row>
     <row r="28" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="773" t="s">
+      <c r="A28" s="676" t="s">
         <v>551</v>
       </c>
-      <c r="B28" s="706"/>
-      <c r="C28" s="706"/>
-      <c r="D28" s="706"/>
-      <c r="E28" s="706"/>
-      <c r="F28" s="706"/>
-      <c r="G28" s="706"/>
-      <c r="H28" s="706"/>
-      <c r="I28" s="706"/>
-      <c r="J28" s="706"/>
-      <c r="K28" s="706"/>
-      <c r="L28" s="706"/>
-      <c r="M28" s="706"/>
-      <c r="N28" s="706"/>
-      <c r="O28" s="706"/>
-      <c r="P28" s="706"/>
-      <c r="Q28" s="706"/>
-      <c r="R28" s="706"/>
-      <c r="S28" s="706"/>
-      <c r="T28" s="706"/>
-      <c r="U28" s="706"/>
-      <c r="V28" s="706"/>
-      <c r="W28" s="706"/>
-      <c r="X28" s="706"/>
-      <c r="Y28" s="706"/>
-      <c r="Z28" s="706"/>
-      <c r="AA28" s="706"/>
-      <c r="AB28" s="706"/>
-      <c r="AC28" s="707"/>
+      <c r="B28" s="677"/>
+      <c r="C28" s="677"/>
+      <c r="D28" s="677"/>
+      <c r="E28" s="677"/>
+      <c r="F28" s="677"/>
+      <c r="G28" s="677"/>
+      <c r="H28" s="677"/>
+      <c r="I28" s="677"/>
+      <c r="J28" s="677"/>
+      <c r="K28" s="677"/>
+      <c r="L28" s="677"/>
+      <c r="M28" s="677"/>
+      <c r="N28" s="677"/>
+      <c r="O28" s="677"/>
+      <c r="P28" s="677"/>
+      <c r="Q28" s="677"/>
+      <c r="R28" s="677"/>
+      <c r="S28" s="677"/>
+      <c r="T28" s="677"/>
+      <c r="U28" s="677"/>
+      <c r="V28" s="677"/>
+      <c r="W28" s="677"/>
+      <c r="X28" s="677"/>
+      <c r="Y28" s="677"/>
+      <c r="Z28" s="677"/>
+      <c r="AA28" s="677"/>
+      <c r="AB28" s="677"/>
+      <c r="AC28" s="678"/>
     </row>
     <row r="29" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="726" t="s">
+      <c r="A29" s="707" t="s">
         <v>551</v>
       </c>
-      <c r="B29" s="729" t="s">
+      <c r="B29" s="693" t="s">
         <v>142</v>
       </c>
-      <c r="C29" s="730" t="s">
+      <c r="C29" s="710" t="s">
         <v>538</v>
       </c>
-      <c r="D29" s="733" t="s">
+      <c r="D29" s="712" t="s">
         <v>402</v>
       </c>
       <c r="E29" s="321" t="s">
@@ -21559,10 +21627,10 @@
       </c>
     </row>
     <row r="30" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="727"/>
-      <c r="B30" s="729"/>
-      <c r="C30" s="731"/>
-      <c r="D30" s="734"/>
+      <c r="A30" s="698"/>
+      <c r="B30" s="693"/>
+      <c r="C30" s="686"/>
+      <c r="D30" s="705"/>
       <c r="E30" s="322" t="s">
         <v>541</v>
       </c>
@@ -21640,10 +21708,10 @@
       </c>
     </row>
     <row r="31" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="728"/>
-      <c r="B31" s="729"/>
-      <c r="C31" s="732"/>
-      <c r="D31" s="735"/>
+      <c r="A31" s="699"/>
+      <c r="B31" s="693"/>
+      <c r="C31" s="715"/>
+      <c r="D31" s="706"/>
       <c r="E31" s="323" t="s">
         <v>542</v>
       </c>
@@ -21721,18 +21789,18 @@
       </c>
     </row>
     <row r="32" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="736" t="str">
+      <c r="A32" s="697" t="str">
         <f>A29</f>
         <v>Storage &amp; Loading Dock</v>
       </c>
-      <c r="B32" s="737" t="str">
+      <c r="B32" s="700" t="str">
         <f>B29</f>
         <v>Ancillary</v>
       </c>
-      <c r="C32" s="738" t="s">
+      <c r="C32" s="733" t="s">
         <v>543</v>
       </c>
-      <c r="D32" s="739" t="s">
+      <c r="D32" s="734" t="s">
         <v>402</v>
       </c>
       <c r="E32" s="324" t="s">
@@ -21812,10 +21880,10 @@
       </c>
     </row>
     <row r="33" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="727"/>
-      <c r="B33" s="729"/>
-      <c r="C33" s="731"/>
-      <c r="D33" s="734"/>
+      <c r="A33" s="698"/>
+      <c r="B33" s="693"/>
+      <c r="C33" s="686"/>
+      <c r="D33" s="705"/>
       <c r="E33" s="325" t="s">
         <v>541</v>
       </c>
@@ -21893,10 +21961,10 @@
       </c>
     </row>
     <row r="34" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="728"/>
-      <c r="B34" s="729"/>
-      <c r="C34" s="732"/>
-      <c r="D34" s="735"/>
+      <c r="A34" s="699"/>
+      <c r="B34" s="693"/>
+      <c r="C34" s="715"/>
+      <c r="D34" s="706"/>
       <c r="E34" s="326" t="s">
         <v>542</v>
       </c>
@@ -21974,18 +22042,18 @@
       </c>
     </row>
     <row r="35" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="740" t="str">
+      <c r="A35" s="679" t="str">
         <f>A29</f>
         <v>Storage &amp; Loading Dock</v>
       </c>
-      <c r="B35" s="774" t="str">
+      <c r="B35" s="682" t="str">
         <f>B29</f>
         <v>Ancillary</v>
       </c>
-      <c r="C35" s="745" t="s">
+      <c r="C35" s="685" t="s">
         <v>545</v>
       </c>
-      <c r="D35" s="720" t="s">
+      <c r="D35" s="688" t="s">
         <v>546</v>
       </c>
       <c r="E35" s="362" t="s">
@@ -22065,10 +22133,10 @@
       </c>
     </row>
     <row r="36" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="741"/>
-      <c r="B36" s="775"/>
-      <c r="C36" s="731"/>
-      <c r="D36" s="721"/>
+      <c r="A36" s="680"/>
+      <c r="B36" s="683"/>
+      <c r="C36" s="686"/>
+      <c r="D36" s="689"/>
       <c r="E36" s="361" t="s">
         <v>541</v>
       </c>
@@ -22146,10 +22214,10 @@
       </c>
     </row>
     <row r="37" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="742"/>
-      <c r="B37" s="776"/>
-      <c r="C37" s="746"/>
-      <c r="D37" s="722"/>
+      <c r="A37" s="681"/>
+      <c r="B37" s="684"/>
+      <c r="C37" s="687"/>
+      <c r="D37" s="690"/>
       <c r="E37" s="366" t="s">
         <v>542</v>
       </c>
@@ -22227,18 +22295,18 @@
       </c>
     </row>
     <row r="38" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="740" t="str">
+      <c r="A38" s="679" t="str">
         <f>A29</f>
         <v>Storage &amp; Loading Dock</v>
       </c>
-      <c r="B38" s="743" t="str">
+      <c r="B38" s="692" t="str">
         <f>B29</f>
         <v>Ancillary</v>
       </c>
-      <c r="C38" s="745" t="s">
+      <c r="C38" s="685" t="s">
         <v>547</v>
       </c>
-      <c r="D38" s="747" t="s">
+      <c r="D38" s="736" t="s">
         <v>402</v>
       </c>
       <c r="E38" s="327" t="s">
@@ -22318,10 +22386,10 @@
       </c>
     </row>
     <row r="39" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="741"/>
-      <c r="B39" s="729"/>
-      <c r="C39" s="731"/>
-      <c r="D39" s="734"/>
+      <c r="A39" s="680"/>
+      <c r="B39" s="693"/>
+      <c r="C39" s="686"/>
+      <c r="D39" s="705"/>
       <c r="E39" s="325" t="s">
         <v>541</v>
       </c>
@@ -22399,10 +22467,10 @@
       </c>
     </row>
     <row r="40" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="742"/>
-      <c r="B40" s="744"/>
-      <c r="C40" s="746"/>
-      <c r="D40" s="748"/>
+      <c r="A40" s="681"/>
+      <c r="B40" s="735"/>
+      <c r="C40" s="687"/>
+      <c r="D40" s="713"/>
       <c r="E40" s="329" t="s">
         <v>542</v>
       </c>
@@ -22480,18 +22548,18 @@
       </c>
     </row>
     <row r="41" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="726" t="str">
+      <c r="A41" s="707" t="str">
         <f>A29</f>
         <v>Storage &amp; Loading Dock</v>
       </c>
-      <c r="B41" s="729" t="str">
+      <c r="B41" s="693" t="str">
         <f>B29</f>
         <v>Ancillary</v>
       </c>
-      <c r="C41" s="730" t="s">
+      <c r="C41" s="710" t="s">
         <v>548</v>
       </c>
-      <c r="D41" s="733" t="s">
+      <c r="D41" s="712" t="s">
         <v>552</v>
       </c>
       <c r="E41" s="330" t="s">
@@ -22571,10 +22639,10 @@
       </c>
     </row>
     <row r="42" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="727"/>
-      <c r="B42" s="729"/>
-      <c r="C42" s="731"/>
-      <c r="D42" s="734"/>
+      <c r="A42" s="698"/>
+      <c r="B42" s="693"/>
+      <c r="C42" s="686"/>
+      <c r="D42" s="705"/>
       <c r="E42" s="325" t="s">
         <v>541</v>
       </c>
@@ -22652,10 +22720,10 @@
       </c>
     </row>
     <row r="43" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="756"/>
-      <c r="B43" s="757"/>
-      <c r="C43" s="758"/>
-      <c r="D43" s="748"/>
+      <c r="A43" s="708"/>
+      <c r="B43" s="709"/>
+      <c r="C43" s="711"/>
+      <c r="D43" s="713"/>
       <c r="E43" s="332" t="s">
         <v>542</v>
       </c>
@@ -22733,18 +22801,18 @@
       </c>
     </row>
     <row r="44" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="726" t="str">
+      <c r="A44" s="707" t="str">
         <f>A32</f>
         <v>Storage &amp; Loading Dock</v>
       </c>
-      <c r="B44" s="737" t="str">
+      <c r="B44" s="700" t="str">
         <f>B29</f>
         <v>Ancillary</v>
       </c>
-      <c r="C44" s="759" t="s">
+      <c r="C44" s="714" t="s">
         <v>239</v>
       </c>
-      <c r="D44" s="733" t="s">
+      <c r="D44" s="712" t="s">
         <v>402</v>
       </c>
       <c r="E44" s="335" t="s">
@@ -22824,10 +22892,10 @@
       </c>
     </row>
     <row r="45" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="727"/>
-      <c r="B45" s="729"/>
-      <c r="C45" s="731"/>
-      <c r="D45" s="734"/>
+      <c r="A45" s="698"/>
+      <c r="B45" s="693"/>
+      <c r="C45" s="686"/>
+      <c r="D45" s="705"/>
       <c r="E45" s="325" t="s">
         <v>541</v>
       </c>
@@ -22905,10 +22973,10 @@
       </c>
     </row>
     <row r="46" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="728"/>
-      <c r="B46" s="757"/>
-      <c r="C46" s="732"/>
-      <c r="D46" s="760"/>
+      <c r="A46" s="699"/>
+      <c r="B46" s="709"/>
+      <c r="C46" s="715"/>
+      <c r="D46" s="716"/>
       <c r="E46" s="326" t="s">
         <v>542</v>
       </c>
@@ -22986,18 +23054,18 @@
       </c>
     </row>
     <row r="47" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="740" t="str">
+      <c r="A47" s="679" t="str">
         <f>A32</f>
         <v>Storage &amp; Loading Dock</v>
       </c>
-      <c r="B47" s="743" t="str">
+      <c r="B47" s="692" t="str">
         <f>B32</f>
         <v>Ancillary</v>
       </c>
-      <c r="C47" s="778" t="s">
+      <c r="C47" s="694" t="s">
         <v>549</v>
       </c>
-      <c r="D47" s="778" t="s">
+      <c r="D47" s="694" t="s">
         <v>553</v>
       </c>
       <c r="E47" s="336" t="s">
@@ -23077,10 +23145,10 @@
       </c>
     </row>
     <row r="48" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="741"/>
-      <c r="B48" s="729"/>
-      <c r="C48" s="779"/>
-      <c r="D48" s="779"/>
+      <c r="A48" s="680"/>
+      <c r="B48" s="693"/>
+      <c r="C48" s="695"/>
+      <c r="D48" s="695"/>
       <c r="E48" s="339" t="s">
         <v>541</v>
       </c>
@@ -23158,10 +23226,10 @@
       </c>
     </row>
     <row r="49" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="777"/>
-      <c r="B49" s="729"/>
-      <c r="C49" s="780"/>
-      <c r="D49" s="780"/>
+      <c r="A49" s="691"/>
+      <c r="B49" s="693"/>
+      <c r="C49" s="696"/>
+      <c r="D49" s="696"/>
       <c r="E49" s="342" t="s">
         <v>542</v>
       </c>
@@ -23239,18 +23307,18 @@
       </c>
     </row>
     <row r="50" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="736" t="str">
+      <c r="A50" s="697" t="str">
         <f>A29</f>
         <v>Storage &amp; Loading Dock</v>
       </c>
-      <c r="B50" s="737" t="str">
+      <c r="B50" s="700" t="str">
         <f>B29</f>
         <v>Ancillary</v>
       </c>
-      <c r="C50" s="781" t="s">
+      <c r="C50" s="701" t="s">
         <v>550</v>
       </c>
-      <c r="D50" s="755" t="s">
+      <c r="D50" s="704" t="s">
         <v>553</v>
       </c>
       <c r="E50" s="343" t="s">
@@ -23330,10 +23398,10 @@
       </c>
     </row>
     <row r="51" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="727"/>
-      <c r="B51" s="729"/>
-      <c r="C51" s="782"/>
-      <c r="D51" s="734"/>
+      <c r="A51" s="698"/>
+      <c r="B51" s="693"/>
+      <c r="C51" s="702"/>
+      <c r="D51" s="705"/>
       <c r="E51" s="346" t="s">
         <v>541</v>
       </c>
@@ -23411,10 +23479,10 @@
       </c>
     </row>
     <row r="52" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="728"/>
-      <c r="B52" s="729"/>
-      <c r="C52" s="783"/>
-      <c r="D52" s="735"/>
+      <c r="A52" s="699"/>
+      <c r="B52" s="693"/>
+      <c r="C52" s="703"/>
+      <c r="D52" s="706"/>
       <c r="E52" s="349" t="s">
         <v>542</v>
       </c>
@@ -23492,16 +23560,16 @@
       </c>
     </row>
     <row r="53" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="761" t="s">
+      <c r="A53" s="664" t="s">
         <v>554</v>
       </c>
-      <c r="B53" s="764" t="s">
+      <c r="B53" s="667" t="s">
         <v>142</v>
       </c>
-      <c r="C53" s="767" t="s">
+      <c r="C53" s="670" t="s">
         <v>555</v>
       </c>
-      <c r="D53" s="770" t="s">
+      <c r="D53" s="673" t="s">
         <v>556</v>
       </c>
       <c r="E53" s="571" t="s">
@@ -23581,10 +23649,10 @@
       </c>
     </row>
     <row r="54" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="762"/>
-      <c r="B54" s="765"/>
-      <c r="C54" s="768"/>
-      <c r="D54" s="771"/>
+      <c r="A54" s="665"/>
+      <c r="B54" s="668"/>
+      <c r="C54" s="671"/>
+      <c r="D54" s="674"/>
       <c r="E54" s="163" t="s">
         <v>541</v>
       </c>
@@ -23662,10 +23730,10 @@
       </c>
     </row>
     <row r="55" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="763"/>
-      <c r="B55" s="766"/>
-      <c r="C55" s="769"/>
-      <c r="D55" s="772"/>
+      <c r="A55" s="666"/>
+      <c r="B55" s="669"/>
+      <c r="C55" s="672"/>
+      <c r="D55" s="675"/>
       <c r="E55" s="137" t="s">
         <v>542</v>
       </c>
@@ -23743,47 +23811,47 @@
       </c>
     </row>
     <row r="56" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="704" t="s">
+      <c r="A56" s="770" t="s">
         <v>557</v>
       </c>
-      <c r="B56" s="705"/>
-      <c r="C56" s="705"/>
-      <c r="D56" s="705"/>
-      <c r="E56" s="706"/>
-      <c r="F56" s="706"/>
-      <c r="G56" s="706"/>
-      <c r="H56" s="706"/>
-      <c r="I56" s="706"/>
-      <c r="J56" s="706"/>
-      <c r="K56" s="706"/>
-      <c r="L56" s="706"/>
-      <c r="M56" s="706"/>
-      <c r="N56" s="706"/>
-      <c r="O56" s="706"/>
-      <c r="P56" s="706"/>
-      <c r="Q56" s="706"/>
-      <c r="R56" s="706"/>
-      <c r="S56" s="706"/>
-      <c r="T56" s="706"/>
-      <c r="U56" s="706"/>
-      <c r="V56" s="706"/>
-      <c r="W56" s="706"/>
-      <c r="X56" s="706"/>
-      <c r="Y56" s="706"/>
-      <c r="Z56" s="706"/>
-      <c r="AA56" s="706"/>
-      <c r="AB56" s="706"/>
-      <c r="AC56" s="707"/>
+      <c r="B56" s="771"/>
+      <c r="C56" s="771"/>
+      <c r="D56" s="771"/>
+      <c r="E56" s="677"/>
+      <c r="F56" s="677"/>
+      <c r="G56" s="677"/>
+      <c r="H56" s="677"/>
+      <c r="I56" s="677"/>
+      <c r="J56" s="677"/>
+      <c r="K56" s="677"/>
+      <c r="L56" s="677"/>
+      <c r="M56" s="677"/>
+      <c r="N56" s="677"/>
+      <c r="O56" s="677"/>
+      <c r="P56" s="677"/>
+      <c r="Q56" s="677"/>
+      <c r="R56" s="677"/>
+      <c r="S56" s="677"/>
+      <c r="T56" s="677"/>
+      <c r="U56" s="677"/>
+      <c r="V56" s="677"/>
+      <c r="W56" s="677"/>
+      <c r="X56" s="677"/>
+      <c r="Y56" s="677"/>
+      <c r="Z56" s="677"/>
+      <c r="AA56" s="677"/>
+      <c r="AB56" s="677"/>
+      <c r="AC56" s="678"/>
     </row>
     <row r="57" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="699"/>
-      <c r="B57" s="684" t="s">
+      <c r="A57" s="764"/>
+      <c r="B57" s="756" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="687" t="s">
+      <c r="C57" s="761" t="s">
         <v>558</v>
       </c>
-      <c r="D57" s="688"/>
+      <c r="D57" s="763"/>
       <c r="E57" s="191" t="s">
         <v>540</v>
       </c>
@@ -23861,10 +23929,10 @@
       </c>
     </row>
     <row r="58" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="700"/>
-      <c r="B58" s="685"/>
-      <c r="C58" s="676"/>
-      <c r="D58" s="688"/>
+      <c r="A58" s="765"/>
+      <c r="B58" s="750"/>
+      <c r="C58" s="762"/>
+      <c r="D58" s="763"/>
       <c r="E58" s="167" t="s">
         <v>541</v>
       </c>
@@ -23942,10 +24010,10 @@
       </c>
     </row>
     <row r="59" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="701"/>
-      <c r="B59" s="702"/>
-      <c r="C59" s="677"/>
-      <c r="D59" s="703"/>
+      <c r="A59" s="766"/>
+      <c r="B59" s="767"/>
+      <c r="C59" s="768"/>
+      <c r="D59" s="769"/>
       <c r="E59" s="168" t="s">
         <v>542</v>
       </c>
@@ -24023,14 +24091,14 @@
       </c>
     </row>
     <row r="60" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="681"/>
-      <c r="B60" s="684" t="s">
+      <c r="A60" s="748"/>
+      <c r="B60" s="756" t="s">
         <v>110</v>
       </c>
-      <c r="C60" s="687" t="s">
+      <c r="C60" s="761" t="s">
         <v>559</v>
       </c>
-      <c r="D60" s="688"/>
+      <c r="D60" s="763"/>
       <c r="E60" s="191" t="s">
         <v>540</v>
       </c>
@@ -24108,10 +24176,10 @@
       </c>
     </row>
     <row r="61" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="682"/>
-      <c r="B61" s="685"/>
-      <c r="C61" s="676"/>
-      <c r="D61" s="688"/>
+      <c r="A61" s="718"/>
+      <c r="B61" s="750"/>
+      <c r="C61" s="762"/>
+      <c r="D61" s="763"/>
       <c r="E61" s="167" t="s">
         <v>541</v>
       </c>
@@ -24189,10 +24257,10 @@
       </c>
     </row>
     <row r="62" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="683"/>
-      <c r="B62" s="686"/>
-      <c r="C62" s="676"/>
-      <c r="D62" s="688"/>
+      <c r="A62" s="737"/>
+      <c r="B62" s="757"/>
+      <c r="C62" s="762"/>
+      <c r="D62" s="763"/>
       <c r="E62" s="192" t="s">
         <v>542</v>
       </c>
@@ -24270,16 +24338,16 @@
       </c>
     </row>
     <row r="63" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="672" t="s">
+      <c r="A63" s="772" t="s">
         <v>560</v>
       </c>
-      <c r="B63" s="675" t="s">
+      <c r="B63" s="739" t="s">
         <v>110</v>
       </c>
-      <c r="C63" s="675" t="s">
+      <c r="C63" s="739" t="s">
         <v>561</v>
       </c>
-      <c r="D63" s="678" t="s">
+      <c r="D63" s="741" t="s">
         <v>562</v>
       </c>
       <c r="E63" s="166" t="s">
@@ -24359,10 +24427,10 @@
       </c>
     </row>
     <row r="64" spans="1:29" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="673"/>
-      <c r="B64" s="676"/>
-      <c r="C64" s="676"/>
-      <c r="D64" s="679"/>
+      <c r="A64" s="773"/>
+      <c r="B64" s="762"/>
+      <c r="C64" s="762"/>
+      <c r="D64" s="742"/>
       <c r="E64" s="167" t="s">
         <v>541</v>
       </c>
@@ -24440,10 +24508,10 @@
       </c>
     </row>
     <row r="65" spans="1:29" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="674"/>
-      <c r="B65" s="677"/>
-      <c r="C65" s="677"/>
-      <c r="D65" s="680"/>
+      <c r="A65" s="774"/>
+      <c r="B65" s="768"/>
+      <c r="C65" s="768"/>
+      <c r="D65" s="775"/>
       <c r="E65" s="168" t="s">
         <v>542</v>
       </c>
@@ -24521,16 +24589,16 @@
       </c>
     </row>
     <row r="66" spans="1:29" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="672" t="s">
+      <c r="A66" s="772" t="s">
         <v>560</v>
       </c>
-      <c r="B66" s="675" t="s">
+      <c r="B66" s="739" t="s">
         <v>110</v>
       </c>
-      <c r="C66" s="675" t="s">
+      <c r="C66" s="739" t="s">
         <v>563</v>
       </c>
-      <c r="D66" s="678" t="s">
+      <c r="D66" s="741" t="s">
         <v>562</v>
       </c>
       <c r="E66" s="166" t="s">
@@ -24610,10 +24678,10 @@
       </c>
     </row>
     <row r="67" spans="1:29" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="673"/>
-      <c r="B67" s="676"/>
-      <c r="C67" s="676"/>
-      <c r="D67" s="679"/>
+      <c r="A67" s="773"/>
+      <c r="B67" s="762"/>
+      <c r="C67" s="762"/>
+      <c r="D67" s="742"/>
       <c r="E67" s="167" t="s">
         <v>541</v>
       </c>
@@ -24691,10 +24759,10 @@
       </c>
     </row>
     <row r="68" spans="1:29" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="674"/>
-      <c r="B68" s="677"/>
-      <c r="C68" s="677"/>
-      <c r="D68" s="680"/>
+      <c r="A68" s="774"/>
+      <c r="B68" s="768"/>
+      <c r="C68" s="768"/>
+      <c r="D68" s="775"/>
       <c r="E68" s="168" t="s">
         <v>542</v>
       </c>
@@ -24773,6 +24841,83 @@
     </row>
   </sheetData>
   <mergeCells count="93">
+    <mergeCell ref="A66:A68"/>
+    <mergeCell ref="B66:B68"/>
+    <mergeCell ref="C66:C68"/>
+    <mergeCell ref="D66:D68"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="B60:B62"/>
+    <mergeCell ref="C60:C62"/>
+    <mergeCell ref="D60:D62"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="B57:B59"/>
+    <mergeCell ref="C57:C59"/>
+    <mergeCell ref="D57:D59"/>
+    <mergeCell ref="A56:AC56"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="F2:AC2"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="B32:B34"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="D38:D40"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="A44:A46"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:D46"/>
     <mergeCell ref="A53:A55"/>
     <mergeCell ref="B53:B55"/>
     <mergeCell ref="C53:C55"/>
@@ -24789,83 +24934,6 @@
     <mergeCell ref="A50:A52"/>
     <mergeCell ref="B50:B52"/>
     <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="A44:A46"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="B32:B34"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="D38:D40"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="C29:C31"/>
-    <mergeCell ref="D29:D31"/>
-    <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D4:D6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="F2:AC2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="B60:B62"/>
-    <mergeCell ref="C60:C62"/>
-    <mergeCell ref="D60:D62"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="A56:AC56"/>
-    <mergeCell ref="A66:A68"/>
-    <mergeCell ref="B66:B68"/>
-    <mergeCell ref="C66:C68"/>
-    <mergeCell ref="D66:D68"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="B63:B65"/>
-    <mergeCell ref="C63:C65"/>
-    <mergeCell ref="D63:D65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -24900,45 +24968,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="785" t="s">
+      <c r="A1" s="777" t="s">
         <v>564</v>
       </c>
-      <c r="B1" s="786"/>
-      <c r="C1" s="786"/>
-      <c r="D1" s="786"/>
-      <c r="E1" s="786"/>
-      <c r="F1" s="786"/>
-      <c r="G1" s="786"/>
-      <c r="H1" s="786"/>
-      <c r="I1" s="786" t="s">
+      <c r="B1" s="778"/>
+      <c r="C1" s="778"/>
+      <c r="D1" s="778"/>
+      <c r="E1" s="778"/>
+      <c r="F1" s="778"/>
+      <c r="G1" s="778"/>
+      <c r="H1" s="778"/>
+      <c r="I1" s="778" t="s">
         <v>565</v>
       </c>
-      <c r="J1" s="786"/>
-      <c r="K1" s="786"/>
-      <c r="L1" s="786"/>
-      <c r="N1" s="584" t="s">
+      <c r="J1" s="778"/>
+      <c r="K1" s="778"/>
+      <c r="L1" s="778"/>
+      <c r="N1" s="581" t="s">
         <v>566</v>
       </c>
-      <c r="O1" s="584"/>
-      <c r="P1" s="584"/>
-      <c r="Q1" s="584"/>
-      <c r="R1" s="584"/>
-      <c r="S1" s="584"/>
-      <c r="T1" s="584"/>
-      <c r="U1" s="584"/>
-      <c r="V1" s="584"/>
-      <c r="Y1" s="600" t="s">
+      <c r="O1" s="581"/>
+      <c r="P1" s="581"/>
+      <c r="Q1" s="581"/>
+      <c r="R1" s="581"/>
+      <c r="S1" s="581"/>
+      <c r="T1" s="581"/>
+      <c r="U1" s="581"/>
+      <c r="V1" s="581"/>
+      <c r="Y1" s="604" t="s">
         <v>567</v>
       </c>
-      <c r="Z1" s="600"/>
-      <c r="AA1" s="600"/>
-      <c r="AB1" s="600"/>
-      <c r="AC1" s="600"/>
-      <c r="AD1" s="600"/>
-      <c r="AE1" s="600"/>
-      <c r="AF1" s="600"/>
-      <c r="AG1" s="600"/>
-      <c r="AH1" s="600"/>
+      <c r="Z1" s="604"/>
+      <c r="AA1" s="604"/>
+      <c r="AB1" s="604"/>
+      <c r="AC1" s="604"/>
+      <c r="AD1" s="604"/>
+      <c r="AE1" s="604"/>
+      <c r="AF1" s="604"/>
+      <c r="AG1" s="604"/>
+      <c r="AH1" s="604"/>
       <c r="AU1" s="2" t="s">
         <v>568</v>
       </c>
@@ -25010,18 +25078,18 @@
       <c r="V2" s="184" t="s">
         <v>585</v>
       </c>
-      <c r="Y2" s="784" t="s">
+      <c r="Y2" s="776" t="s">
         <v>586</v>
       </c>
-      <c r="Z2" s="784"/>
-      <c r="AA2" s="784"/>
-      <c r="AB2" s="784"/>
-      <c r="AC2" s="784"/>
-      <c r="AD2" s="784"/>
-      <c r="AE2" s="784"/>
-      <c r="AF2" s="784"/>
-      <c r="AG2" s="784"/>
-      <c r="AH2" s="784"/>
+      <c r="Z2" s="776"/>
+      <c r="AA2" s="776"/>
+      <c r="AB2" s="776"/>
+      <c r="AC2" s="776"/>
+      <c r="AD2" s="776"/>
+      <c r="AE2" s="776"/>
+      <c r="AF2" s="776"/>
+      <c r="AG2" s="776"/>
+      <c r="AH2" s="776"/>
       <c r="AJ2" s="187" t="s">
         <v>587</v>
       </c>
@@ -25037,7 +25105,7 @@
       </c>
     </row>
     <row r="3" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="589" t="s">
+      <c r="A3" s="587" t="s">
         <v>59</v>
       </c>
       <c r="B3" s="555">
@@ -25064,7 +25132,7 @@
         <f>J3-K3</f>
         <v>23.400000000000006</v>
       </c>
-      <c r="N3" s="629" t="s">
+      <c r="N3" s="619" t="s">
         <v>127</v>
       </c>
       <c r="O3" s="185">
@@ -25105,7 +25173,7 @@
       </c>
     </row>
     <row r="4" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="589"/>
+      <c r="A4" s="587"/>
       <c r="B4" s="555">
         <v>2</v>
       </c>
@@ -25130,7 +25198,7 @@
         <f t="shared" ref="L4:L18" si="5">J4-K4</f>
         <v>29.200000000000003</v>
       </c>
-      <c r="N4" s="629"/>
+      <c r="N4" s="619"/>
       <c r="O4" s="185">
         <v>2</v>
       </c>
@@ -25169,7 +25237,7 @@
       </c>
     </row>
     <row r="5" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="589"/>
+      <c r="A5" s="587"/>
       <c r="B5" s="555">
         <v>3</v>
       </c>
@@ -25194,7 +25262,7 @@
         <f t="shared" si="5"/>
         <v>26.150000000000006</v>
       </c>
-      <c r="N5" s="629"/>
+      <c r="N5" s="619"/>
       <c r="O5" s="185">
         <v>3</v>
       </c>
@@ -25224,7 +25292,7 @@
       </c>
     </row>
     <row r="6" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="589"/>
+      <c r="A6" s="587"/>
       <c r="B6" s="555">
         <v>4</v>
       </c>
@@ -25249,7 +25317,7 @@
         <f t="shared" si="5"/>
         <v>30.450000000000003</v>
       </c>
-      <c r="N6" s="629"/>
+      <c r="N6" s="619"/>
       <c r="O6" s="185">
         <v>4</v>
       </c>
@@ -25279,7 +25347,7 @@
       </c>
     </row>
     <row r="7" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="589"/>
+      <c r="A7" s="587"/>
       <c r="B7" s="555">
         <v>5</v>
       </c>
@@ -25304,7 +25372,7 @@
         <f t="shared" si="5"/>
         <v>25.200000000000003</v>
       </c>
-      <c r="N7" s="629"/>
+      <c r="N7" s="619"/>
       <c r="O7" s="185">
         <v>5</v>
       </c>
@@ -25334,7 +25402,7 @@
       </c>
     </row>
     <row r="8" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="589"/>
+      <c r="A8" s="587"/>
       <c r="B8" s="555">
         <v>6</v>
       </c>
@@ -25359,7 +25427,7 @@
         <f t="shared" si="5"/>
         <v>28.900000000000006</v>
       </c>
-      <c r="N8" s="629"/>
+      <c r="N8" s="619"/>
       <c r="O8" s="185">
         <v>6</v>
       </c>
@@ -25389,7 +25457,7 @@
       </c>
     </row>
     <row r="9" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="589"/>
+      <c r="A9" s="587"/>
       <c r="B9" s="555">
         <v>7</v>
       </c>
@@ -25414,7 +25482,7 @@
         <f t="shared" si="5"/>
         <v>28.900000000000006</v>
       </c>
-      <c r="N9" s="629"/>
+      <c r="N9" s="619"/>
       <c r="O9" s="185">
         <v>7</v>
       </c>
@@ -25444,7 +25512,7 @@
       </c>
     </row>
     <row r="10" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="589"/>
+      <c r="A10" s="587"/>
       <c r="B10" s="555">
         <v>8</v>
       </c>
@@ -25469,7 +25537,7 @@
         <f t="shared" si="5"/>
         <v>29.450000000000003</v>
       </c>
-      <c r="N10" s="629"/>
+      <c r="N10" s="619"/>
       <c r="O10" s="185">
         <v>8</v>
       </c>
@@ -25499,7 +25567,7 @@
       </c>
     </row>
     <row r="11" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="589"/>
+      <c r="A11" s="587"/>
       <c r="B11" s="555">
         <v>9</v>
       </c>
@@ -25524,7 +25592,7 @@
         <f t="shared" si="5"/>
         <v>29.799999999999997</v>
       </c>
-      <c r="N11" s="629"/>
+      <c r="N11" s="619"/>
       <c r="O11" s="185">
         <v>9</v>
       </c>
@@ -25554,7 +25622,7 @@
       </c>
     </row>
     <row r="12" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="589"/>
+      <c r="A12" s="587"/>
       <c r="B12" s="555">
         <v>10</v>
       </c>
@@ -25579,7 +25647,7 @@
         <f t="shared" si="5"/>
         <v>30.099999999999994</v>
       </c>
-      <c r="N12" s="629"/>
+      <c r="N12" s="619"/>
       <c r="O12" s="185">
         <v>10</v>
       </c>
@@ -25609,7 +25677,7 @@
       </c>
     </row>
     <row r="13" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="589"/>
+      <c r="A13" s="587"/>
       <c r="B13" s="555">
         <v>11</v>
       </c>
@@ -25634,7 +25702,7 @@
         <f t="shared" si="5"/>
         <v>31.150000000000006</v>
       </c>
-      <c r="N13" s="629"/>
+      <c r="N13" s="619"/>
       <c r="O13" s="185">
         <v>11</v>
       </c>
@@ -25664,7 +25732,7 @@
       </c>
     </row>
     <row r="14" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="589"/>
+      <c r="A14" s="587"/>
       <c r="B14" s="555">
         <v>12</v>
       </c>
@@ -25689,7 +25757,7 @@
         <f t="shared" si="5"/>
         <v>30.650000000000006</v>
       </c>
-      <c r="N14" s="629"/>
+      <c r="N14" s="619"/>
       <c r="O14" s="185">
         <v>12</v>
       </c>
@@ -25719,7 +25787,7 @@
       </c>
     </row>
     <row r="15" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="589"/>
+      <c r="A15" s="587"/>
       <c r="B15" s="555">
         <v>13</v>
       </c>
@@ -25744,7 +25812,7 @@
         <f t="shared" si="5"/>
         <v>31.150000000000006</v>
       </c>
-      <c r="N15" s="629"/>
+      <c r="N15" s="619"/>
       <c r="O15" s="185">
         <v>13</v>
       </c>
@@ -25774,7 +25842,7 @@
       </c>
     </row>
     <row r="16" spans="1:48" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="589"/>
+      <c r="A16" s="587"/>
       <c r="B16" s="555">
         <v>14</v>
       </c>
@@ -25799,7 +25867,7 @@
         <f t="shared" si="5"/>
         <v>31.299999999999997</v>
       </c>
-      <c r="N16" s="629"/>
+      <c r="N16" s="619"/>
       <c r="O16" s="185">
         <v>14</v>
       </c>
@@ -25829,7 +25897,7 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="589"/>
+      <c r="A17" s="587"/>
       <c r="B17" s="555">
         <v>15</v>
       </c>
@@ -25854,7 +25922,7 @@
         <f t="shared" si="5"/>
         <v>30.049999999999997</v>
       </c>
-      <c r="N17" s="629"/>
+      <c r="N17" s="619"/>
       <c r="O17" s="185">
         <v>15</v>
       </c>
@@ -25884,7 +25952,7 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="589"/>
+      <c r="A18" s="587"/>
       <c r="B18" s="555">
         <v>16</v>
       </c>
@@ -25909,7 +25977,7 @@
         <f t="shared" si="5"/>
         <v>30.599999999999994</v>
       </c>
-      <c r="N18" s="629"/>
+      <c r="N18" s="619"/>
       <c r="O18" s="185">
         <v>16</v>
       </c>
@@ -25995,80 +26063,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="28.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="615" t="str">
+      <c r="A1" s="599" t="str">
         <f>"% of Floor Area per CZ and Vintage Bin - Retail"</f>
         <v>% of Floor Area per CZ and Vintage Bin - Retail</v>
       </c>
-      <c r="B1" s="615"/>
-      <c r="C1" s="615"/>
-      <c r="D1" s="615"/>
-      <c r="E1" s="615"/>
-      <c r="F1" s="615"/>
-      <c r="G1" s="615"/>
-      <c r="J1" s="615" t="str">
+      <c r="B1" s="599"/>
+      <c r="C1" s="599"/>
+      <c r="D1" s="599"/>
+      <c r="E1" s="599"/>
+      <c r="F1" s="599"/>
+      <c r="G1" s="599"/>
+      <c r="J1" s="599" t="str">
         <f>"% of Floor Area per CZ and Vintage Bin - Retail"</f>
         <v>% of Floor Area per CZ and Vintage Bin - Retail</v>
       </c>
-      <c r="K1" s="615"/>
-      <c r="L1" s="615"/>
-      <c r="M1" s="615"/>
-      <c r="N1" s="615"/>
-      <c r="O1" s="615"/>
-      <c r="P1" s="615"/>
-      <c r="Q1" s="615"/>
-      <c r="R1" s="615"/>
-      <c r="S1" s="615"/>
-      <c r="T1" s="615"/>
-      <c r="U1" s="615"/>
-      <c r="V1" s="615"/>
-      <c r="W1" s="615"/>
-      <c r="X1" s="615"/>
-      <c r="Y1" s="615"/>
-      <c r="Z1" s="615"/>
-      <c r="AA1" s="615"/>
+      <c r="K1" s="599"/>
+      <c r="L1" s="599"/>
+      <c r="M1" s="599"/>
+      <c r="N1" s="599"/>
+      <c r="O1" s="599"/>
+      <c r="P1" s="599"/>
+      <c r="Q1" s="599"/>
+      <c r="R1" s="599"/>
+      <c r="S1" s="599"/>
+      <c r="T1" s="599"/>
+      <c r="U1" s="599"/>
+      <c r="V1" s="599"/>
+      <c r="W1" s="599"/>
+      <c r="X1" s="599"/>
+      <c r="Y1" s="599"/>
+      <c r="Z1" s="599"/>
+      <c r="AA1" s="599"/>
     </row>
     <row r="2" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="793" t="s">
+      <c r="A2" s="785" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="793" t="s">
+      <c r="B2" s="785" t="s">
         <v>570</v>
       </c>
-      <c r="C2" s="793" t="s">
+      <c r="C2" s="785" t="s">
         <v>593</v>
       </c>
-      <c r="D2" s="793"/>
-      <c r="E2" s="793"/>
-      <c r="F2" s="793"/>
-      <c r="G2" s="793"/>
-      <c r="J2" s="793" t="s">
+      <c r="D2" s="785"/>
+      <c r="E2" s="785"/>
+      <c r="F2" s="785"/>
+      <c r="G2" s="785"/>
+      <c r="J2" s="785" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="793" t="s">
+      <c r="K2" s="785" t="s">
         <v>593</v>
       </c>
-      <c r="L2" s="793" t="s">
+      <c r="L2" s="785" t="s">
         <v>570</v>
       </c>
-      <c r="M2" s="793"/>
-      <c r="N2" s="793"/>
-      <c r="O2" s="793"/>
-      <c r="P2" s="793"/>
-      <c r="Q2" s="793"/>
-      <c r="R2" s="793"/>
-      <c r="S2" s="793"/>
-      <c r="T2" s="793"/>
-      <c r="U2" s="793"/>
-      <c r="V2" s="793"/>
-      <c r="W2" s="793"/>
-      <c r="X2" s="793"/>
-      <c r="Y2" s="793"/>
-      <c r="Z2" s="793"/>
-      <c r="AA2" s="793"/>
+      <c r="M2" s="785"/>
+      <c r="N2" s="785"/>
+      <c r="O2" s="785"/>
+      <c r="P2" s="785"/>
+      <c r="Q2" s="785"/>
+      <c r="R2" s="785"/>
+      <c r="S2" s="785"/>
+      <c r="T2" s="785"/>
+      <c r="U2" s="785"/>
+      <c r="V2" s="785"/>
+      <c r="W2" s="785"/>
+      <c r="X2" s="785"/>
+      <c r="Y2" s="785"/>
+      <c r="Z2" s="785"/>
+      <c r="AA2" s="785"/>
     </row>
     <row r="3" spans="1:28" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="793"/>
-      <c r="B3" s="793"/>
+      <c r="A3" s="785"/>
+      <c r="B3" s="785"/>
       <c r="C3" s="548" t="s">
         <v>594</v>
       </c>
@@ -26084,8 +26152,8 @@
       <c r="G3" s="548" t="s">
         <v>595</v>
       </c>
-      <c r="J3" s="793"/>
-      <c r="K3" s="793"/>
+      <c r="J3" s="785"/>
+      <c r="K3" s="785"/>
       <c r="L3" s="548">
         <v>1</v>
       </c>
@@ -26136,7 +26204,7 @@
       </c>
     </row>
     <row r="4" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="790" t="s">
+      <c r="A4" s="782" t="s">
         <v>127</v>
       </c>
       <c r="B4" s="100">
@@ -26151,7 +26219,7 @@
         <f t="shared" ref="H4:H20" si="0">SUM(C4:F4)</f>
         <v>0</v>
       </c>
-      <c r="J4" s="787" t="s">
+      <c r="J4" s="779" t="s">
         <v>127</v>
       </c>
       <c r="K4" s="34" t="s">
@@ -26179,7 +26247,7 @@
       </c>
     </row>
     <row r="5" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="791"/>
+      <c r="A5" s="783"/>
       <c r="B5" s="31">
         <v>2</v>
       </c>
@@ -26192,7 +26260,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J5" s="788"/>
+      <c r="J5" s="780"/>
       <c r="K5" s="34" t="s">
         <v>211</v>
       </c>
@@ -26218,7 +26286,7 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="791"/>
+      <c r="A6" s="783"/>
       <c r="B6" s="31">
         <v>3</v>
       </c>
@@ -26231,7 +26299,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J6" s="788"/>
+      <c r="J6" s="780"/>
       <c r="K6" s="34" t="s">
         <v>213</v>
       </c>
@@ -26257,7 +26325,7 @@
       </c>
     </row>
     <row r="7" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="791"/>
+      <c r="A7" s="783"/>
       <c r="B7" s="31">
         <v>4</v>
       </c>
@@ -26270,7 +26338,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J7" s="788"/>
+      <c r="J7" s="780"/>
       <c r="K7" s="34" t="s">
         <v>215</v>
       </c>
@@ -26296,7 +26364,7 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="791"/>
+      <c r="A8" s="783"/>
       <c r="B8" s="31">
         <v>5</v>
       </c>
@@ -26309,7 +26377,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="788"/>
+      <c r="J8" s="780"/>
       <c r="K8" s="34" t="s">
         <v>595</v>
       </c>
@@ -26335,7 +26403,7 @@
       </c>
     </row>
     <row r="9" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="791"/>
+      <c r="A9" s="783"/>
       <c r="B9" s="31">
         <v>6</v>
       </c>
@@ -26348,7 +26416,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J9" s="789"/>
+      <c r="J9" s="781"/>
       <c r="K9" s="34" t="s">
         <v>163</v>
       </c>
@@ -26374,7 +26442,7 @@
       </c>
     </row>
     <row r="10" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="791"/>
+      <c r="A10" s="783"/>
       <c r="B10" s="31">
         <v>7</v>
       </c>
@@ -26396,7 +26464,7 @@
       <c r="P10" s="59"/>
     </row>
     <row r="11" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="791"/>
+      <c r="A11" s="783"/>
       <c r="B11" s="31">
         <v>8</v>
       </c>
@@ -26418,7 +26486,7 @@
       <c r="P11" s="59"/>
     </row>
     <row r="12" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="791"/>
+      <c r="A12" s="783"/>
       <c r="B12" s="31">
         <v>9</v>
       </c>
@@ -26440,7 +26508,7 @@
       <c r="P12" s="59"/>
     </row>
     <row r="13" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="791"/>
+      <c r="A13" s="783"/>
       <c r="B13" s="31">
         <v>10</v>
       </c>
@@ -26462,7 +26530,7 @@
       <c r="P13" s="59"/>
     </row>
     <row r="14" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="791"/>
+      <c r="A14" s="783"/>
       <c r="B14" s="31">
         <v>11</v>
       </c>
@@ -26484,7 +26552,7 @@
       <c r="P14" s="59"/>
     </row>
     <row r="15" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="791"/>
+      <c r="A15" s="783"/>
       <c r="B15" s="31">
         <v>12</v>
       </c>
@@ -26506,7 +26574,7 @@
       <c r="P15" s="59"/>
     </row>
     <row r="16" spans="1:28" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="791"/>
+      <c r="A16" s="783"/>
       <c r="B16" s="31">
         <v>13</v>
       </c>
@@ -26528,7 +26596,7 @@
       <c r="P16" s="59"/>
     </row>
     <row r="17" spans="1:16" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="791"/>
+      <c r="A17" s="783"/>
       <c r="B17" s="31">
         <v>14</v>
       </c>
@@ -26550,7 +26618,7 @@
       <c r="P17" s="59"/>
     </row>
     <row r="18" spans="1:16" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="791"/>
+      <c r="A18" s="783"/>
       <c r="B18" s="31">
         <v>15</v>
       </c>
@@ -26572,7 +26640,7 @@
       <c r="P18" s="59"/>
     </row>
     <row r="19" spans="1:16" ht="16.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="791"/>
+      <c r="A19" s="783"/>
       <c r="B19" s="31">
         <v>16</v>
       </c>
@@ -26594,7 +26662,7 @@
       <c r="P19" s="59"/>
     </row>
     <row r="20" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="792"/>
+      <c r="A20" s="784"/>
       <c r="B20" s="108" t="s">
         <v>596</v>
       </c>
@@ -26652,19 +26720,19 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="615" t="str">
+      <c r="A1" s="599" t="str">
         <f>"PV - "&amp;Prototype!A2</f>
         <v>PV - RetailMedium</v>
       </c>
-      <c r="B1" s="615"/>
-      <c r="C1" s="615"/>
-      <c r="D1" s="615"/>
-      <c r="E1" s="615"/>
-      <c r="F1" s="615"/>
-      <c r="G1" s="615"/>
-      <c r="H1" s="615"/>
-      <c r="I1" s="615"/>
-      <c r="J1" s="615"/>
+      <c r="B1" s="599"/>
+      <c r="C1" s="599"/>
+      <c r="D1" s="599"/>
+      <c r="E1" s="599"/>
+      <c r="F1" s="599"/>
+      <c r="G1" s="599"/>
+      <c r="H1" s="599"/>
+      <c r="I1" s="599"/>
+      <c r="J1" s="599"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -26719,17 +26787,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="615" t="str">
+      <c r="A1" s="599" t="str">
         <f>"EV Charger - "&amp;Prototype!A2</f>
         <v>EV Charger - RetailMedium</v>
       </c>
-      <c r="B1" s="615"/>
-      <c r="C1" s="615"/>
-      <c r="D1" s="615"/>
-      <c r="E1" s="615"/>
-      <c r="F1" s="615"/>
-      <c r="G1" s="615"/>
-      <c r="H1" s="615"/>
+      <c r="B1" s="599"/>
+      <c r="C1" s="599"/>
+      <c r="D1" s="599"/>
+      <c r="E1" s="599"/>
+      <c r="F1" s="599"/>
+      <c r="G1" s="599"/>
+      <c r="H1" s="599"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -26783,12 +26851,12 @@
       <c r="C1" t="s">
         <v>600</v>
       </c>
-      <c r="D1" s="794" t="s">
+      <c r="D1" s="786" t="s">
         <v>601</v>
       </c>
-      <c r="E1" s="794"/>
-      <c r="F1" s="794"/>
-      <c r="G1" s="794"/>
+      <c r="E1" s="786"/>
+      <c r="F1" s="786"/>
+      <c r="G1" s="786"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="551" t="s">
@@ -27692,23 +27760,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="584" t="str">
+      <c r="A1" s="581" t="str">
         <f>"Proposed Layout - "&amp;Prototype!A2</f>
         <v>Proposed Layout - RetailMedium</v>
       </c>
-      <c r="B1" s="584"/>
-      <c r="C1" s="584"/>
-      <c r="D1" s="584"/>
-      <c r="E1" s="584"/>
-      <c r="F1" s="584"/>
-      <c r="G1" s="584"/>
-      <c r="H1" s="584"/>
-      <c r="I1" s="584"/>
-      <c r="J1" s="584"/>
-      <c r="K1" s="584"/>
-      <c r="L1" s="584"/>
-      <c r="M1" s="584"/>
-      <c r="N1" s="584"/>
+      <c r="B1" s="581"/>
+      <c r="C1" s="581"/>
+      <c r="D1" s="581"/>
+      <c r="E1" s="581"/>
+      <c r="F1" s="581"/>
+      <c r="G1" s="581"/>
+      <c r="H1" s="581"/>
+      <c r="I1" s="581"/>
+      <c r="J1" s="581"/>
+      <c r="K1" s="581"/>
+      <c r="L1" s="581"/>
+      <c r="M1" s="581"/>
+      <c r="N1" s="581"/>
       <c r="Q1" s="3" t="s">
         <v>109</v>
       </c>
@@ -28277,12 +28345,12 @@
       <c r="M16" s="550"/>
       <c r="N16" s="550"/>
       <c r="O16" s="550"/>
-      <c r="P16" s="589" t="str">
+      <c r="P16" s="587" t="str">
         <f>C3</f>
         <v>Retail Sales Area (Retail Merchandise Sales)</v>
       </c>
-      <c r="Q16" s="589"/>
-      <c r="R16" s="589"/>
+      <c r="Q16" s="587"/>
+      <c r="R16" s="587"/>
       <c r="S16" s="410">
         <f>SUM(H3:H5)</f>
         <v>0.83000000000000007</v>
@@ -28301,12 +28369,12 @@
       <c r="M17" s="550"/>
       <c r="N17" s="550"/>
       <c r="O17" s="550"/>
-      <c r="P17" s="589" t="str">
+      <c r="P17" s="587" t="str">
         <f>C6</f>
         <v>Corridor Area</v>
       </c>
-      <c r="Q17" s="589"/>
-      <c r="R17" s="589"/>
+      <c r="Q17" s="587"/>
+      <c r="R17" s="587"/>
       <c r="S17" s="410">
         <f>H6</f>
         <v>5.0000000000000001E-3</v>
@@ -28324,12 +28392,12 @@
       <c r="M18" s="550"/>
       <c r="N18" s="550"/>
       <c r="O18" s="550"/>
-      <c r="P18" s="589" t="str">
+      <c r="P18" s="587" t="str">
         <f>C7</f>
         <v>Storage, Commercial/Industrial (Shipping &amp; Handling)</v>
       </c>
-      <c r="Q18" s="589"/>
-      <c r="R18" s="589"/>
+      <c r="Q18" s="587"/>
+      <c r="R18" s="587"/>
       <c r="S18" s="410">
         <f>H7</f>
         <v>2.4E-2</v>
@@ -28347,12 +28415,12 @@
       <c r="M19" s="550"/>
       <c r="N19" s="550"/>
       <c r="O19" s="550"/>
-      <c r="P19" s="589" t="str">
+      <c r="P19" s="587" t="str">
         <f>C8</f>
         <v>Storage (General)</v>
       </c>
-      <c r="Q19" s="589"/>
-      <c r="R19" s="589"/>
+      <c r="Q19" s="587"/>
+      <c r="R19" s="587"/>
       <c r="S19" s="410">
         <f>H8</f>
         <v>9.7000000000000003E-2</v>
@@ -28370,12 +28438,12 @@
       <c r="M20" s="550"/>
       <c r="N20" s="550"/>
       <c r="O20" s="550"/>
-      <c r="P20" s="589" t="str">
+      <c r="P20" s="587" t="str">
         <f>C9</f>
         <v>Office Area (&gt;250 square feet)</v>
       </c>
-      <c r="Q20" s="589"/>
-      <c r="R20" s="589"/>
+      <c r="Q20" s="587"/>
+      <c r="R20" s="587"/>
       <c r="S20" s="410">
         <f>H9</f>
         <v>2.7E-2</v>
@@ -28393,12 +28461,12 @@
       <c r="M21" s="550"/>
       <c r="N21" s="550"/>
       <c r="O21" s="550"/>
-      <c r="P21" s="589" t="str">
+      <c r="P21" s="587" t="str">
         <f>C10</f>
         <v>Restrooms</v>
       </c>
-      <c r="Q21" s="589"/>
-      <c r="R21" s="589"/>
+      <c r="Q21" s="587"/>
+      <c r="R21" s="587"/>
       <c r="S21" s="410">
         <f>H10</f>
         <v>1.7000000000000001E-2</v>
@@ -28457,11 +28525,11 @@
       </c>
     </row>
     <row r="27" spans="3:20" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="587" t="s">
+      <c r="C27" s="589" t="s">
         <v>165</v>
       </c>
-      <c r="D27" s="587"/>
-      <c r="E27" s="587"/>
+      <c r="D27" s="589"/>
+      <c r="E27" s="589"/>
     </row>
     <row r="28" spans="3:20" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="62" t="s">
@@ -28639,17 +28707,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="P22:R22"/>
     <mergeCell ref="C27:E27"/>
     <mergeCell ref="P14:S14"/>
     <mergeCell ref="P15:R15"/>
     <mergeCell ref="P16:R16"/>
     <mergeCell ref="P17:R17"/>
     <mergeCell ref="P18:R18"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="P22:R22"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28717,33 +28785,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="615" t="str">
+      <c r="A1" s="599" t="str">
         <f>"Envelope - "&amp;Prototype!A2</f>
         <v>Envelope - RetailMedium</v>
       </c>
-      <c r="B1" s="615"/>
-      <c r="C1" s="615"/>
-      <c r="D1" s="615"/>
-      <c r="E1" s="615"/>
-      <c r="F1" s="615"/>
-      <c r="G1" s="615"/>
-      <c r="H1" s="615"/>
-      <c r="I1" s="615"/>
-      <c r="J1" s="615"/>
-      <c r="K1" s="615"/>
-      <c r="L1" s="615"/>
-      <c r="M1" s="615"/>
-      <c r="N1" s="615"/>
-      <c r="O1" s="615"/>
-      <c r="P1" s="615"/>
-      <c r="Q1" s="615"/>
-      <c r="R1" s="615"/>
-      <c r="S1" s="615"/>
-      <c r="T1" s="615"/>
-      <c r="U1" s="615"/>
-      <c r="V1" s="615"/>
-      <c r="W1" s="615"/>
-      <c r="X1" s="615"/>
+      <c r="B1" s="599"/>
+      <c r="C1" s="599"/>
+      <c r="D1" s="599"/>
+      <c r="E1" s="599"/>
+      <c r="F1" s="599"/>
+      <c r="G1" s="599"/>
+      <c r="H1" s="599"/>
+      <c r="I1" s="599"/>
+      <c r="J1" s="599"/>
+      <c r="K1" s="599"/>
+      <c r="L1" s="599"/>
+      <c r="M1" s="599"/>
+      <c r="N1" s="599"/>
+      <c r="O1" s="599"/>
+      <c r="P1" s="599"/>
+      <c r="Q1" s="599"/>
+      <c r="R1" s="599"/>
+      <c r="S1" s="599"/>
+      <c r="T1" s="599"/>
+      <c r="U1" s="599"/>
+      <c r="V1" s="599"/>
+      <c r="W1" s="599"/>
+      <c r="X1" s="599"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
@@ -28824,19 +28892,19 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="592" t="s">
+      <c r="A3" s="590" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="592" t="s">
+      <c r="B3" s="590" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="593" t="s">
+      <c r="C3" s="595" t="s">
         <v>206</v>
       </c>
-      <c r="D3" s="617" t="s">
+      <c r="D3" s="600" t="s">
         <v>207</v>
       </c>
-      <c r="E3" s="592" t="s">
+      <c r="E3" s="590" t="s">
         <v>208</v>
       </c>
       <c r="F3" s="558" t="s">
@@ -28898,11 +28966,11 @@
       </c>
     </row>
     <row r="4" spans="1:26" s="1" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="592"/>
-      <c r="B4" s="592"/>
-      <c r="C4" s="593"/>
-      <c r="D4" s="593"/>
-      <c r="E4" s="592"/>
+      <c r="A4" s="590"/>
+      <c r="B4" s="590"/>
+      <c r="C4" s="595"/>
+      <c r="D4" s="595"/>
+      <c r="E4" s="590"/>
       <c r="F4" s="378" t="s">
         <v>211</v>
       </c>
@@ -28964,11 +29032,11 @@
       <c r="Z4" s="76"/>
     </row>
     <row r="5" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="592"/>
-      <c r="B5" s="592"/>
-      <c r="C5" s="593"/>
-      <c r="D5" s="593"/>
-      <c r="E5" s="592"/>
+      <c r="A5" s="590"/>
+      <c r="B5" s="590"/>
+      <c r="C5" s="595"/>
+      <c r="D5" s="595"/>
+      <c r="E5" s="590"/>
       <c r="F5" s="83" t="s">
         <v>213</v>
       </c>
@@ -29030,11 +29098,11 @@
       <c r="Z5" s="78"/>
     </row>
     <row r="6" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="592"/>
-      <c r="B6" s="592"/>
-      <c r="C6" s="593"/>
-      <c r="D6" s="593"/>
-      <c r="E6" s="592"/>
+      <c r="A6" s="590"/>
+      <c r="B6" s="590"/>
+      <c r="C6" s="595"/>
+      <c r="D6" s="595"/>
+      <c r="E6" s="590"/>
       <c r="F6" s="374" t="s">
         <v>215</v>
       </c>
@@ -29096,11 +29164,11 @@
       <c r="Z6" s="78"/>
     </row>
     <row r="7" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="592"/>
-      <c r="B7" s="592"/>
-      <c r="C7" s="593"/>
-      <c r="D7" s="593"/>
-      <c r="E7" s="592"/>
+      <c r="A7" s="590"/>
+      <c r="B7" s="590"/>
+      <c r="C7" s="595"/>
+      <c r="D7" s="595"/>
+      <c r="E7" s="590"/>
       <c r="F7" s="370" t="s">
         <v>218</v>
       </c>
@@ -29162,19 +29230,19 @@
       <c r="Z7" s="78"/>
     </row>
     <row r="8" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="592" t="s">
+      <c r="A8" s="590" t="s">
         <v>219</v>
       </c>
-      <c r="B8" s="592" t="s">
+      <c r="B8" s="590" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="593" t="s">
+      <c r="C8" s="595" t="s">
         <v>220</v>
       </c>
-      <c r="D8" s="621" t="s">
+      <c r="D8" s="594" t="s">
         <v>221</v>
       </c>
-      <c r="E8" s="592" t="s">
+      <c r="E8" s="590" t="s">
         <v>208</v>
       </c>
       <c r="F8" s="558" t="s">
@@ -29183,7 +29251,7 @@
       <c r="G8" s="558" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="590" t="s">
+      <c r="H8" s="591" t="s">
         <v>222</v>
       </c>
       <c r="I8" s="80">
@@ -29238,18 +29306,18 @@
       <c r="Z8" s="78"/>
     </row>
     <row r="9" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="592"/>
-      <c r="B9" s="592"/>
-      <c r="C9" s="593"/>
-      <c r="D9" s="621"/>
-      <c r="E9" s="592"/>
+      <c r="A9" s="590"/>
+      <c r="B9" s="590"/>
+      <c r="C9" s="595"/>
+      <c r="D9" s="594"/>
+      <c r="E9" s="590"/>
       <c r="F9" s="378" t="s">
         <v>211</v>
       </c>
       <c r="G9" s="378">
         <v>1992</v>
       </c>
-      <c r="H9" s="591"/>
+      <c r="H9" s="593"/>
       <c r="I9" s="81">
         <v>5.7000000000000002E-2</v>
       </c>
@@ -29302,11 +29370,11 @@
       <c r="Z9" s="78"/>
     </row>
     <row r="10" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="592"/>
-      <c r="B10" s="592"/>
-      <c r="C10" s="593"/>
-      <c r="D10" s="621"/>
-      <c r="E10" s="592"/>
+      <c r="A10" s="590"/>
+      <c r="B10" s="590"/>
+      <c r="C10" s="595"/>
+      <c r="D10" s="594"/>
+      <c r="E10" s="590"/>
       <c r="F10" s="83" t="s">
         <v>213</v>
       </c>
@@ -29368,11 +29436,11 @@
       <c r="Z10" s="78"/>
     </row>
     <row r="11" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="592"/>
-      <c r="B11" s="592"/>
-      <c r="C11" s="593"/>
-      <c r="D11" s="621"/>
-      <c r="E11" s="592"/>
+      <c r="A11" s="590"/>
+      <c r="B11" s="590"/>
+      <c r="C11" s="595"/>
+      <c r="D11" s="594"/>
+      <c r="E11" s="590"/>
       <c r="F11" s="373" t="s">
         <v>215</v>
       </c>
@@ -29434,11 +29502,11 @@
       <c r="Z11" s="78"/>
     </row>
     <row r="12" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="592"/>
-      <c r="B12" s="592"/>
-      <c r="C12" s="593"/>
-      <c r="D12" s="621"/>
-      <c r="E12" s="592"/>
+      <c r="A12" s="590"/>
+      <c r="B12" s="590"/>
+      <c r="C12" s="595"/>
+      <c r="D12" s="594"/>
+      <c r="E12" s="590"/>
       <c r="F12" s="370" t="s">
         <v>218</v>
       </c>
@@ -29500,19 +29568,19 @@
       <c r="Z12" s="78"/>
     </row>
     <row r="13" spans="1:26" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="592" t="s">
+      <c r="A13" s="590" t="s">
         <v>223</v>
       </c>
-      <c r="B13" s="592" t="s">
+      <c r="B13" s="590" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="590" t="s">
+      <c r="C13" s="591" t="s">
         <v>224</v>
       </c>
-      <c r="D13" s="593" t="s">
+      <c r="D13" s="595" t="s">
         <v>225</v>
       </c>
-      <c r="E13" s="592" t="s">
+      <c r="E13" s="590" t="s">
         <v>208</v>
       </c>
       <c r="F13" s="558" t="s">
@@ -29521,7 +29589,7 @@
       <c r="G13" s="558" t="s">
         <v>87</v>
       </c>
-      <c r="H13" s="590" t="s">
+      <c r="H13" s="591" t="s">
         <v>226</v>
       </c>
       <c r="I13" s="558">
@@ -29592,18 +29660,18 @@
       <c r="Z13" s="78"/>
     </row>
     <row r="14" spans="1:26" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="592"/>
-      <c r="B14" s="592"/>
-      <c r="C14" s="616"/>
-      <c r="D14" s="593"/>
-      <c r="E14" s="592"/>
+      <c r="A14" s="590"/>
+      <c r="B14" s="590"/>
+      <c r="C14" s="592"/>
+      <c r="D14" s="595"/>
+      <c r="E14" s="590"/>
       <c r="F14" s="378" t="s">
         <v>211</v>
       </c>
       <c r="G14" s="378" t="s">
         <v>87</v>
       </c>
-      <c r="H14" s="591"/>
+      <c r="H14" s="593"/>
       <c r="I14" s="82">
         <f>I13</f>
         <v>0.74</v>
@@ -29672,13 +29740,13 @@
       <c r="Z14" s="78"/>
     </row>
     <row r="15" spans="1:26" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="592"/>
-      <c r="B15" s="592"/>
-      <c r="C15" s="616"/>
-      <c r="D15" s="592" t="s">
+      <c r="A15" s="590"/>
+      <c r="B15" s="590"/>
+      <c r="C15" s="592"/>
+      <c r="D15" s="590" t="s">
         <v>227</v>
       </c>
-      <c r="E15" s="592"/>
+      <c r="E15" s="590"/>
       <c r="F15" s="83" t="s">
         <v>213</v>
       </c>
@@ -29740,11 +29808,11 @@
       <c r="Z15" s="78"/>
     </row>
     <row r="16" spans="1:26" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="592"/>
-      <c r="B16" s="592"/>
-      <c r="C16" s="616"/>
-      <c r="D16" s="592"/>
-      <c r="E16" s="592"/>
+      <c r="A16" s="590"/>
+      <c r="B16" s="590"/>
+      <c r="C16" s="592"/>
+      <c r="D16" s="590"/>
+      <c r="E16" s="590"/>
       <c r="F16" s="374" t="s">
         <v>215</v>
       </c>
@@ -29806,11 +29874,11 @@
       <c r="Z16" s="78"/>
     </row>
     <row r="17" spans="1:63" s="1" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="592"/>
-      <c r="B17" s="592"/>
-      <c r="C17" s="591"/>
-      <c r="D17" s="592"/>
-      <c r="E17" s="592"/>
+      <c r="A17" s="590"/>
+      <c r="B17" s="590"/>
+      <c r="C17" s="593"/>
+      <c r="D17" s="590"/>
+      <c r="E17" s="590"/>
       <c r="F17" s="370" t="s">
         <v>218</v>
       </c>
@@ -29872,17 +29940,17 @@
       <c r="Z17" s="78"/>
     </row>
     <row r="18" spans="1:63" s="1" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="592"/>
-      <c r="B18" s="592" t="s">
+      <c r="A18" s="590"/>
+      <c r="B18" s="590" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="590" t="s">
+      <c r="C18" s="591" t="s">
         <v>224</v>
       </c>
-      <c r="D18" s="593" t="s">
+      <c r="D18" s="595" t="s">
         <v>225</v>
       </c>
-      <c r="E18" s="592" t="s">
+      <c r="E18" s="590" t="s">
         <v>229</v>
       </c>
       <c r="F18" s="558" t="s">
@@ -29891,7 +29959,7 @@
       <c r="G18" s="558" t="s">
         <v>87</v>
       </c>
-      <c r="H18" s="590" t="s">
+      <c r="H18" s="591" t="s">
         <v>230</v>
       </c>
       <c r="I18" s="413">
@@ -29962,18 +30030,18 @@
       <c r="Z18" s="78"/>
     </row>
     <row r="19" spans="1:63" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="592"/>
-      <c r="B19" s="592"/>
-      <c r="C19" s="616"/>
-      <c r="D19" s="593"/>
-      <c r="E19" s="592"/>
+      <c r="A19" s="590"/>
+      <c r="B19" s="590"/>
+      <c r="C19" s="592"/>
+      <c r="D19" s="595"/>
+      <c r="E19" s="590"/>
       <c r="F19" s="378" t="s">
         <v>211</v>
       </c>
       <c r="G19" s="378" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="591"/>
+      <c r="H19" s="593"/>
       <c r="I19" s="414">
         <f>I18</f>
         <v>0.52</v>
@@ -30042,13 +30110,13 @@
       <c r="Z19" s="78"/>
     </row>
     <row r="20" spans="1:63" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A20" s="592"/>
-      <c r="B20" s="592"/>
-      <c r="C20" s="616"/>
-      <c r="D20" s="592" t="s">
+      <c r="A20" s="590"/>
+      <c r="B20" s="590"/>
+      <c r="C20" s="592"/>
+      <c r="D20" s="590" t="s">
         <v>227</v>
       </c>
-      <c r="E20" s="592"/>
+      <c r="E20" s="590"/>
       <c r="F20" s="376" t="s">
         <v>213</v>
       </c>
@@ -30110,11 +30178,11 @@
       <c r="Z20" s="78"/>
     </row>
     <row r="21" spans="1:63" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="592"/>
-      <c r="B21" s="592"/>
-      <c r="C21" s="616"/>
-      <c r="D21" s="592"/>
-      <c r="E21" s="592"/>
+      <c r="A21" s="590"/>
+      <c r="B21" s="590"/>
+      <c r="C21" s="592"/>
+      <c r="D21" s="590"/>
+      <c r="E21" s="590"/>
       <c r="F21" s="374" t="s">
         <v>215</v>
       </c>
@@ -30176,11 +30244,11 @@
       <c r="Z21" s="78"/>
     </row>
     <row r="22" spans="1:63" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A22" s="592"/>
-      <c r="B22" s="592"/>
-      <c r="C22" s="591"/>
-      <c r="D22" s="592"/>
-      <c r="E22" s="592"/>
+      <c r="A22" s="590"/>
+      <c r="B22" s="590"/>
+      <c r="C22" s="593"/>
+      <c r="D22" s="590"/>
+      <c r="E22" s="590"/>
       <c r="F22" s="370" t="s">
         <v>218</v>
       </c>
@@ -30242,19 +30310,19 @@
       <c r="Z22" s="78"/>
     </row>
     <row r="23" spans="1:63" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="592" t="s">
+      <c r="A23" s="590" t="s">
         <v>232</v>
       </c>
-      <c r="B23" s="592" t="s">
+      <c r="B23" s="590" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="593" t="s">
+      <c r="C23" s="595" t="s">
         <v>232</v>
       </c>
-      <c r="D23" s="590" t="s">
+      <c r="D23" s="591" t="s">
         <v>233</v>
       </c>
-      <c r="E23" s="592" t="s">
+      <c r="E23" s="590" t="s">
         <v>208</v>
       </c>
       <c r="F23" s="558" t="s">
@@ -30263,7 +30331,7 @@
       <c r="G23" s="558" t="s">
         <v>87</v>
       </c>
-      <c r="H23" s="590" t="s">
+      <c r="H23" s="591" t="s">
         <v>234</v>
       </c>
       <c r="I23" s="558">
@@ -30355,18 +30423,18 @@
       <c r="BK23" s="1"/>
     </row>
     <row r="24" spans="1:63" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="592"/>
-      <c r="B24" s="592"/>
-      <c r="C24" s="593"/>
-      <c r="D24" s="591"/>
-      <c r="E24" s="592"/>
+      <c r="A24" s="590"/>
+      <c r="B24" s="590"/>
+      <c r="C24" s="595"/>
+      <c r="D24" s="593"/>
+      <c r="E24" s="590"/>
       <c r="F24" s="378" t="s">
         <v>211</v>
       </c>
       <c r="G24" s="378" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="591"/>
+      <c r="H24" s="593"/>
       <c r="I24" s="82">
         <v>0.85</v>
       </c>
@@ -30456,13 +30524,13 @@
       <c r="BK24" s="1"/>
     </row>
     <row r="25" spans="1:63" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="592"/>
-      <c r="B25" s="592"/>
-      <c r="C25" s="593"/>
-      <c r="D25" s="594" t="s">
+      <c r="A25" s="590"/>
+      <c r="B25" s="590"/>
+      <c r="C25" s="595"/>
+      <c r="D25" s="611" t="s">
         <v>235</v>
       </c>
-      <c r="E25" s="592"/>
+      <c r="E25" s="590"/>
       <c r="F25" s="83" t="s">
         <v>213</v>
       </c>
@@ -30561,11 +30629,11 @@
       <c r="BK25" s="1"/>
     </row>
     <row r="26" spans="1:63" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="592"/>
-      <c r="B26" s="592"/>
-      <c r="C26" s="593"/>
-      <c r="D26" s="595"/>
-      <c r="E26" s="592"/>
+      <c r="A26" s="590"/>
+      <c r="B26" s="590"/>
+      <c r="C26" s="595"/>
+      <c r="D26" s="612"/>
+      <c r="E26" s="590"/>
       <c r="F26" s="374" t="s">
         <v>215</v>
       </c>
@@ -30664,11 +30732,11 @@
       <c r="BK26" s="1"/>
     </row>
     <row r="27" spans="1:63" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="592"/>
-      <c r="B27" s="592"/>
-      <c r="C27" s="593"/>
-      <c r="D27" s="596"/>
-      <c r="E27" s="592"/>
+      <c r="A27" s="590"/>
+      <c r="B27" s="590"/>
+      <c r="C27" s="595"/>
+      <c r="D27" s="613"/>
+      <c r="E27" s="590"/>
       <c r="F27" s="370" t="s">
         <v>218</v>
       </c>
@@ -30767,17 +30835,17 @@
       <c r="BK27" s="1"/>
     </row>
     <row r="28" spans="1:63" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="592"/>
-      <c r="B28" s="592" t="s">
+      <c r="A28" s="590"/>
+      <c r="B28" s="590" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="593" t="s">
+      <c r="C28" s="595" t="s">
         <v>232</v>
       </c>
-      <c r="D28" s="590" t="s">
+      <c r="D28" s="591" t="s">
         <v>233</v>
       </c>
-      <c r="E28" s="592" t="s">
+      <c r="E28" s="590" t="s">
         <v>229</v>
       </c>
       <c r="F28" s="558" t="s">
@@ -30786,7 +30854,7 @@
       <c r="G28" s="558" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="590" t="s">
+      <c r="H28" s="591" t="s">
         <v>236</v>
       </c>
       <c r="I28" s="413">
@@ -30894,18 +30962,18 @@
       <c r="BK28" s="1"/>
     </row>
     <row r="29" spans="1:63" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="592"/>
-      <c r="B29" s="592"/>
-      <c r="C29" s="593"/>
-      <c r="D29" s="591"/>
-      <c r="E29" s="592"/>
+      <c r="A29" s="590"/>
+      <c r="B29" s="590"/>
+      <c r="C29" s="595"/>
+      <c r="D29" s="593"/>
+      <c r="E29" s="590"/>
       <c r="F29" s="378" t="s">
         <v>211</v>
       </c>
       <c r="G29" s="378" t="s">
         <v>87</v>
       </c>
-      <c r="H29" s="591"/>
+      <c r="H29" s="593"/>
       <c r="I29" s="415">
         <f>0.81*0.87</f>
         <v>0.70469999999999999</v>
@@ -31011,13 +31079,13 @@
       <c r="BK29" s="1"/>
     </row>
     <row r="30" spans="1:63" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="592"/>
-      <c r="B30" s="592"/>
-      <c r="C30" s="593"/>
-      <c r="D30" s="594" t="s">
+      <c r="A30" s="590"/>
+      <c r="B30" s="590"/>
+      <c r="C30" s="595"/>
+      <c r="D30" s="611" t="s">
         <v>235</v>
       </c>
-      <c r="E30" s="592"/>
+      <c r="E30" s="590"/>
       <c r="F30" s="376" t="s">
         <v>213</v>
       </c>
@@ -31116,11 +31184,11 @@
       <c r="BK30" s="1"/>
     </row>
     <row r="31" spans="1:63" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="592"/>
-      <c r="B31" s="592"/>
-      <c r="C31" s="593"/>
-      <c r="D31" s="595"/>
-      <c r="E31" s="592"/>
+      <c r="A31" s="590"/>
+      <c r="B31" s="590"/>
+      <c r="C31" s="595"/>
+      <c r="D31" s="612"/>
+      <c r="E31" s="590"/>
       <c r="F31" s="374" t="s">
         <v>215</v>
       </c>
@@ -31219,11 +31287,11 @@
       <c r="BK31" s="1"/>
     </row>
     <row r="32" spans="1:63" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="592"/>
-      <c r="B32" s="592"/>
-      <c r="C32" s="593"/>
-      <c r="D32" s="596"/>
-      <c r="E32" s="592"/>
+      <c r="A32" s="590"/>
+      <c r="B32" s="590"/>
+      <c r="C32" s="595"/>
+      <c r="D32" s="613"/>
+      <c r="E32" s="590"/>
       <c r="F32" s="370" t="s">
         <v>218</v>
       </c>
@@ -31452,30 +31520,30 @@
     <row r="35" spans="1:63" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="599" t="s">
+      <c r="C35" s="603" t="s">
         <v>239</v>
       </c>
-      <c r="D35" s="599"/>
-      <c r="E35" s="599"/>
-      <c r="F35" s="599"/>
-      <c r="G35" s="599"/>
-      <c r="H35" s="599"/>
-      <c r="I35" s="599"/>
-      <c r="J35" s="599"/>
-      <c r="K35" s="599"/>
-      <c r="L35" s="599"/>
-      <c r="M35" s="599"/>
-      <c r="N35" s="599"/>
-      <c r="O35" s="599"/>
-      <c r="P35" s="599"/>
-      <c r="Q35" s="599"/>
-      <c r="R35" s="599"/>
-      <c r="S35" s="599"/>
-      <c r="T35" s="599"/>
-      <c r="U35" s="599"/>
-      <c r="V35" s="599"/>
-      <c r="W35" s="599"/>
-      <c r="X35" s="599"/>
+      <c r="D35" s="603"/>
+      <c r="E35" s="603"/>
+      <c r="F35" s="603"/>
+      <c r="G35" s="603"/>
+      <c r="H35" s="603"/>
+      <c r="I35" s="603"/>
+      <c r="J35" s="603"/>
+      <c r="K35" s="603"/>
+      <c r="L35" s="603"/>
+      <c r="M35" s="603"/>
+      <c r="N35" s="603"/>
+      <c r="O35" s="603"/>
+      <c r="P35" s="603"/>
+      <c r="Q35" s="603"/>
+      <c r="R35" s="603"/>
+      <c r="S35" s="603"/>
+      <c r="T35" s="603"/>
+      <c r="U35" s="603"/>
+      <c r="V35" s="603"/>
+      <c r="W35" s="603"/>
+      <c r="X35" s="603"/>
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
@@ -31535,24 +31603,24 @@
       <c r="H36" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="I36" s="601" t="s">
+      <c r="I36" s="605" t="s">
         <v>242</v>
       </c>
-      <c r="J36" s="602"/>
-      <c r="K36" s="602"/>
-      <c r="L36" s="602"/>
-      <c r="M36" s="602"/>
-      <c r="N36" s="602"/>
-      <c r="O36" s="602"/>
-      <c r="P36" s="602"/>
-      <c r="Q36" s="602"/>
-      <c r="R36" s="602"/>
-      <c r="S36" s="602"/>
-      <c r="T36" s="602"/>
-      <c r="U36" s="602"/>
-      <c r="V36" s="602"/>
-      <c r="W36" s="602"/>
-      <c r="X36" s="603"/>
+      <c r="J36" s="606"/>
+      <c r="K36" s="606"/>
+      <c r="L36" s="606"/>
+      <c r="M36" s="606"/>
+      <c r="N36" s="606"/>
+      <c r="O36" s="606"/>
+      <c r="P36" s="606"/>
+      <c r="Q36" s="606"/>
+      <c r="R36" s="606"/>
+      <c r="S36" s="606"/>
+      <c r="T36" s="606"/>
+      <c r="U36" s="606"/>
+      <c r="V36" s="606"/>
+      <c r="W36" s="606"/>
+      <c r="X36" s="607"/>
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
@@ -31596,13 +31664,13 @@
     <row r="37" spans="1:63" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="609" t="s">
+      <c r="C37" s="596" t="s">
         <v>239</v>
       </c>
-      <c r="D37" s="609" t="s">
+      <c r="D37" s="596" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="609"/>
+      <c r="E37" s="596"/>
       <c r="F37" s="558" t="s">
         <v>209</v>
       </c>
@@ -31612,25 +31680,24 @@
       <c r="H37" s="64" t="s">
         <v>243</v>
       </c>
-      <c r="I37" s="606" t="e">
-        <f>(G37*0.112)*#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J37" s="607"/>
-      <c r="K37" s="607"/>
-      <c r="L37" s="607"/>
-      <c r="M37" s="607"/>
-      <c r="N37" s="607"/>
-      <c r="O37" s="607"/>
-      <c r="P37" s="607"/>
-      <c r="Q37" s="607"/>
-      <c r="R37" s="607"/>
-      <c r="S37" s="607"/>
-      <c r="T37" s="607"/>
-      <c r="U37" s="607"/>
-      <c r="V37" s="607"/>
-      <c r="W37" s="607"/>
-      <c r="X37" s="608"/>
+      <c r="I37" s="787">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="J37" s="788"/>
+      <c r="K37" s="788"/>
+      <c r="L37" s="788"/>
+      <c r="M37" s="788"/>
+      <c r="N37" s="788"/>
+      <c r="O37" s="788"/>
+      <c r="P37" s="788"/>
+      <c r="Q37" s="788"/>
+      <c r="R37" s="788"/>
+      <c r="S37" s="788"/>
+      <c r="T37" s="788"/>
+      <c r="U37" s="788"/>
+      <c r="V37" s="788"/>
+      <c r="W37" s="788"/>
+      <c r="X37" s="791"/>
       <c r="Y37" s="1"/>
       <c r="Z37" s="105" t="s">
         <v>244</v>
@@ -31679,9 +31746,9 @@
     <row r="38" spans="1:63" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="610"/>
-      <c r="D38" s="610"/>
-      <c r="E38" s="610"/>
+      <c r="C38" s="597"/>
+      <c r="D38" s="597"/>
+      <c r="E38" s="597"/>
       <c r="F38" s="558" t="s">
         <v>211</v>
       </c>
@@ -31691,25 +31758,24 @@
       <c r="H38" s="64" t="s">
         <v>243</v>
       </c>
-      <c r="I38" s="606" t="e">
-        <f>(G38*0.112)*#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J38" s="607"/>
-      <c r="K38" s="607"/>
-      <c r="L38" s="607"/>
-      <c r="M38" s="607"/>
-      <c r="N38" s="607"/>
-      <c r="O38" s="607"/>
-      <c r="P38" s="607"/>
-      <c r="Q38" s="607"/>
-      <c r="R38" s="607"/>
-      <c r="S38" s="607"/>
-      <c r="T38" s="607"/>
-      <c r="U38" s="607"/>
-      <c r="V38" s="607"/>
-      <c r="W38" s="607"/>
-      <c r="X38" s="608"/>
+      <c r="I38" s="789">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="J38" s="790"/>
+      <c r="K38" s="790"/>
+      <c r="L38" s="790"/>
+      <c r="M38" s="790"/>
+      <c r="N38" s="790"/>
+      <c r="O38" s="790"/>
+      <c r="P38" s="790"/>
+      <c r="Q38" s="790"/>
+      <c r="R38" s="790"/>
+      <c r="S38" s="790"/>
+      <c r="T38" s="790"/>
+      <c r="U38" s="790"/>
+      <c r="V38" s="790"/>
+      <c r="W38" s="790"/>
+      <c r="X38" s="792"/>
       <c r="Y38" s="1"/>
       <c r="Z38" s="105" t="s">
         <v>245</v>
@@ -31758,9 +31824,9 @@
     <row r="39" spans="1:63" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="610"/>
-      <c r="D39" s="610"/>
-      <c r="E39" s="610"/>
+      <c r="C39" s="597"/>
+      <c r="D39" s="597"/>
+      <c r="E39" s="597"/>
       <c r="F39" s="558" t="s">
         <v>213</v>
       </c>
@@ -31770,25 +31836,24 @@
       <c r="H39" s="64" t="s">
         <v>243</v>
       </c>
-      <c r="I39" s="606" t="e">
-        <f>(G39*0.112)*#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J39" s="607"/>
-      <c r="K39" s="607"/>
-      <c r="L39" s="607"/>
-      <c r="M39" s="607"/>
-      <c r="N39" s="607"/>
-      <c r="O39" s="607"/>
-      <c r="P39" s="607"/>
-      <c r="Q39" s="607"/>
-      <c r="R39" s="607"/>
-      <c r="S39" s="607"/>
-      <c r="T39" s="607"/>
-      <c r="U39" s="607"/>
-      <c r="V39" s="607"/>
-      <c r="W39" s="607"/>
-      <c r="X39" s="608"/>
+      <c r="I39" s="789">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="J39" s="790"/>
+      <c r="K39" s="790"/>
+      <c r="L39" s="790"/>
+      <c r="M39" s="790"/>
+      <c r="N39" s="790"/>
+      <c r="O39" s="790"/>
+      <c r="P39" s="790"/>
+      <c r="Q39" s="790"/>
+      <c r="R39" s="790"/>
+      <c r="S39" s="790"/>
+      <c r="T39" s="790"/>
+      <c r="U39" s="790"/>
+      <c r="V39" s="790"/>
+      <c r="W39" s="790"/>
+      <c r="X39" s="792"/>
       <c r="Y39" s="54"/>
       <c r="Z39" s="105" t="s">
         <v>246</v>
@@ -31817,10 +31882,10 @@
       <c r="AS39" s="1"/>
       <c r="AT39" s="1"/>
       <c r="AU39" s="1"/>
-      <c r="AV39" s="600"/>
-      <c r="AW39" s="600"/>
-      <c r="AX39" s="600"/>
-      <c r="AY39" s="600"/>
+      <c r="AV39" s="604"/>
+      <c r="AW39" s="604"/>
+      <c r="AX39" s="604"/>
+      <c r="AY39" s="604"/>
       <c r="AZ39" s="1"/>
       <c r="BA39" s="1"/>
       <c r="BB39" s="1"/>
@@ -31837,9 +31902,9 @@
     <row r="40" spans="1:63" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="610"/>
-      <c r="D40" s="610"/>
-      <c r="E40" s="610"/>
+      <c r="C40" s="597"/>
+      <c r="D40" s="597"/>
+      <c r="E40" s="597"/>
       <c r="F40" s="558" t="s">
         <v>215</v>
       </c>
@@ -31849,25 +31914,24 @@
       <c r="H40" s="559" t="s">
         <v>247</v>
       </c>
-      <c r="I40" s="606" t="e">
-        <f>(G40*0.112)*#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J40" s="607"/>
-      <c r="K40" s="607"/>
-      <c r="L40" s="607"/>
-      <c r="M40" s="607"/>
-      <c r="N40" s="607"/>
-      <c r="O40" s="607"/>
-      <c r="P40" s="607"/>
-      <c r="Q40" s="607"/>
-      <c r="R40" s="607"/>
-      <c r="S40" s="607"/>
-      <c r="T40" s="607"/>
-      <c r="U40" s="607"/>
-      <c r="V40" s="607"/>
-      <c r="W40" s="607"/>
-      <c r="X40" s="608"/>
+      <c r="I40" s="789">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="J40" s="790"/>
+      <c r="K40" s="790"/>
+      <c r="L40" s="790"/>
+      <c r="M40" s="790"/>
+      <c r="N40" s="790"/>
+      <c r="O40" s="790"/>
+      <c r="P40" s="790"/>
+      <c r="Q40" s="790"/>
+      <c r="R40" s="790"/>
+      <c r="S40" s="790"/>
+      <c r="T40" s="790"/>
+      <c r="U40" s="790"/>
+      <c r="V40" s="790"/>
+      <c r="W40" s="790"/>
+      <c r="X40" s="792"/>
       <c r="Y40" s="1"/>
       <c r="Z40" s="105" t="s">
         <v>248</v>
@@ -31916,9 +31980,9 @@
     <row r="41" spans="1:63" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="611"/>
-      <c r="D41" s="611"/>
-      <c r="E41" s="611"/>
+      <c r="C41" s="598"/>
+      <c r="D41" s="598"/>
+      <c r="E41" s="598"/>
       <c r="F41" s="558" t="s">
         <v>218</v>
       </c>
@@ -31928,25 +31992,24 @@
       <c r="H41" s="559" t="s">
         <v>250</v>
       </c>
-      <c r="I41" s="606" t="e">
-        <f>(0.6*0.112)*#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J41" s="607"/>
-      <c r="K41" s="607"/>
-      <c r="L41" s="607"/>
-      <c r="M41" s="607"/>
-      <c r="N41" s="607"/>
-      <c r="O41" s="607"/>
-      <c r="P41" s="607"/>
-      <c r="Q41" s="607"/>
-      <c r="R41" s="607"/>
-      <c r="S41" s="607"/>
-      <c r="T41" s="607"/>
-      <c r="U41" s="607"/>
-      <c r="V41" s="607"/>
-      <c r="W41" s="607"/>
-      <c r="X41" s="608"/>
+      <c r="I41" s="789">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="J41" s="790"/>
+      <c r="K41" s="790"/>
+      <c r="L41" s="790"/>
+      <c r="M41" s="790"/>
+      <c r="N41" s="790"/>
+      <c r="O41" s="790"/>
+      <c r="P41" s="790"/>
+      <c r="Q41" s="790"/>
+      <c r="R41" s="790"/>
+      <c r="S41" s="790"/>
+      <c r="T41" s="790"/>
+      <c r="U41" s="790"/>
+      <c r="V41" s="790"/>
+      <c r="W41" s="790"/>
+      <c r="X41" s="792"/>
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
@@ -32252,22 +32315,22 @@
       <c r="BK45" s="1"/>
     </row>
     <row r="46" spans="1:63" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="618" t="s">
+      <c r="A46" s="793" t="s">
         <v>252</v>
       </c>
-      <c r="B46" s="619"/>
-      <c r="C46" s="619"/>
-      <c r="D46" s="619"/>
-      <c r="E46" s="620"/>
+      <c r="B46" s="794"/>
+      <c r="C46" s="794"/>
+      <c r="D46" s="794"/>
+      <c r="E46" s="795"/>
       <c r="F46" s="76"/>
       <c r="G46" s="270"/>
-      <c r="H46" s="604" t="s">
+      <c r="H46" s="796" t="s">
         <v>253</v>
       </c>
-      <c r="I46" s="605"/>
-      <c r="J46" s="605"/>
-      <c r="K46" s="605"/>
-      <c r="L46" s="605"/>
+      <c r="I46" s="797"/>
+      <c r="J46" s="797"/>
+      <c r="K46" s="797"/>
+      <c r="L46" s="797"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
@@ -32613,10 +32676,10 @@
       <c r="M50" s="557"/>
       <c r="N50" s="557"/>
       <c r="O50" s="557"/>
-      <c r="P50" s="600"/>
-      <c r="Q50" s="600"/>
-      <c r="R50" s="600"/>
-      <c r="S50" s="600"/>
+      <c r="P50" s="604"/>
+      <c r="Q50" s="604"/>
+      <c r="R50" s="604"/>
+      <c r="S50" s="604"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
@@ -33446,10 +33509,10 @@
       <c r="BK60" s="1"/>
     </row>
     <row r="61" spans="1:63" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="612"/>
-      <c r="B61" s="613"/>
-      <c r="C61" s="613"/>
-      <c r="D61" s="614"/>
+      <c r="A61" s="608"/>
+      <c r="B61" s="609"/>
+      <c r="C61" s="609"/>
+      <c r="D61" s="610"/>
       <c r="E61" s="76"/>
       <c r="F61" s="76"/>
       <c r="G61" s="270"/>
@@ -33593,7 +33656,7 @@
       <c r="C63" s="447">
         <v>0.09</v>
       </c>
-      <c r="D63" s="597" t="s">
+      <c r="D63" s="601" t="s">
         <v>325</v>
       </c>
       <c r="E63" s="76"/>
@@ -33666,7 +33729,7 @@
       <c r="C64" s="447">
         <v>0.18</v>
       </c>
-      <c r="D64" s="597"/>
+      <c r="D64" s="601"/>
       <c r="E64" s="76"/>
       <c r="F64" s="76"/>
       <c r="G64" s="270"/>
@@ -33737,7 +33800,7 @@
       <c r="C65" s="447">
         <v>0.28000000000000003</v>
       </c>
-      <c r="D65" s="597"/>
+      <c r="D65" s="601"/>
       <c r="E65" s="76"/>
       <c r="F65" s="76"/>
       <c r="G65" s="270"/>
@@ -33808,7 +33871,7 @@
       <c r="C66" s="449">
         <v>0.37</v>
       </c>
-      <c r="D66" s="598"/>
+      <c r="D66" s="602"/>
       <c r="E66" s="76"/>
       <c r="F66" s="76"/>
       <c r="G66" s="270"/>
@@ -35561,18 +35624,32 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="E13:E17"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="A23:A32"/>
+    <mergeCell ref="B23:B27"/>
+    <mergeCell ref="C23:C27"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="D25:D27"/>
+    <mergeCell ref="B28:B32"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="C35:X35"/>
+    <mergeCell ref="AV39:AY39"/>
+    <mergeCell ref="I36:X36"/>
+    <mergeCell ref="H46:L46"/>
+    <mergeCell ref="I41:X41"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="I38:X38"/>
+    <mergeCell ref="I39:X39"/>
+    <mergeCell ref="I40:X40"/>
+    <mergeCell ref="I37:X37"/>
+    <mergeCell ref="P50:S50"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="C18:C22"/>
     <mergeCell ref="E18:E22"/>
@@ -35589,32 +35666,18 @@
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="H18:H19"/>
-    <mergeCell ref="D63:D66"/>
-    <mergeCell ref="C35:X35"/>
-    <mergeCell ref="AV39:AY39"/>
-    <mergeCell ref="I36:X36"/>
-    <mergeCell ref="H46:L46"/>
-    <mergeCell ref="I41:X41"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="I38:X38"/>
-    <mergeCell ref="I39:X39"/>
-    <mergeCell ref="I40:X40"/>
-    <mergeCell ref="I37:X37"/>
-    <mergeCell ref="P50:S50"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="H28:H29"/>
-    <mergeCell ref="A23:A32"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="C23:C27"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="E23:E27"/>
-    <mergeCell ref="D25:D27"/>
-    <mergeCell ref="B28:B32"/>
-    <mergeCell ref="C28:C32"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E32"/>
-    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="D37:D41"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
@@ -35656,16 +35719,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="626" t="str">
+      <c r="A1" s="622" t="str">
         <f>"HVAC system - "&amp;Prototype!A2</f>
         <v>HVAC system - RetailMedium</v>
       </c>
-      <c r="B1" s="626"/>
-      <c r="C1" s="626"/>
-      <c r="D1" s="626"/>
-      <c r="E1" s="626"/>
-      <c r="F1" s="626"/>
-      <c r="G1" s="626"/>
+      <c r="B1" s="622"/>
+      <c r="C1" s="622"/>
+      <c r="D1" s="622"/>
+      <c r="E1" s="622"/>
+      <c r="F1" s="622"/>
+      <c r="G1" s="622"/>
     </row>
     <row r="2" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="570" t="s">
@@ -35764,13 +35827,13 @@
       <c r="E7" s="547"/>
     </row>
     <row r="8" spans="1:10" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="627" t="s">
+      <c r="A8" s="623" t="s">
         <v>350</v>
       </c>
-      <c r="B8" s="628"/>
-      <c r="C8" s="628"/>
-      <c r="D8" s="628"/>
-      <c r="E8" s="628"/>
+      <c r="B8" s="624"/>
+      <c r="C8" s="624"/>
+      <c r="D8" s="624"/>
+      <c r="E8" s="624"/>
     </row>
     <row r="9" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
@@ -35793,16 +35856,16 @@
       <c r="A10" s="558" t="s">
         <v>209</v>
       </c>
-      <c r="B10" s="590">
+      <c r="B10" s="591">
         <v>2008</v>
       </c>
-      <c r="C10" s="629" t="s">
+      <c r="C10" s="619" t="s">
         <v>352</v>
       </c>
-      <c r="D10" s="624" t="s">
+      <c r="D10" s="617" t="s">
         <v>353</v>
       </c>
-      <c r="E10" s="624" t="s">
+      <c r="E10" s="617" t="s">
         <v>354</v>
       </c>
     </row>
@@ -35810,19 +35873,19 @@
       <c r="A11" s="558" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="616"/>
-      <c r="C11" s="629"/>
-      <c r="D11" s="623"/>
-      <c r="E11" s="623"/>
+      <c r="B11" s="592"/>
+      <c r="C11" s="619"/>
+      <c r="D11" s="625"/>
+      <c r="E11" s="625"/>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="558" t="s">
         <v>213</v>
       </c>
-      <c r="B12" s="591"/>
-      <c r="C12" s="629"/>
-      <c r="D12" s="623"/>
-      <c r="E12" s="623"/>
+      <c r="B12" s="593"/>
+      <c r="C12" s="619"/>
+      <c r="D12" s="625"/>
+      <c r="E12" s="625"/>
     </row>
     <row r="13" spans="1:10" ht="60.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="558" t="s">
@@ -35882,17 +35945,17 @@
       <c r="E17" s="553"/>
     </row>
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="630" t="s">
+      <c r="A18" s="614" t="s">
         <v>363</v>
       </c>
-      <c r="B18" s="630"/>
-      <c r="C18" s="630"/>
-      <c r="D18" s="630"/>
-      <c r="E18" s="630"/>
-      <c r="F18" s="630"/>
-      <c r="G18" s="630"/>
-      <c r="H18" s="631"/>
-      <c r="I18" s="632"/>
+      <c r="B18" s="614"/>
+      <c r="C18" s="614"/>
+      <c r="D18" s="614"/>
+      <c r="E18" s="614"/>
+      <c r="F18" s="614"/>
+      <c r="G18" s="614"/>
+      <c r="H18" s="615"/>
+      <c r="I18" s="616"/>
     </row>
     <row r="19" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="310" t="s">
@@ -35924,10 +35987,10 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="629" t="s">
+      <c r="A20" s="619" t="s">
         <v>217</v>
       </c>
-      <c r="B20" s="622" t="s">
+      <c r="B20" s="626" t="s">
         <v>371</v>
       </c>
       <c r="C20" s="560" t="s">
@@ -35936,31 +35999,31 @@
       <c r="D20" s="560">
         <v>2.5</v>
       </c>
-      <c r="E20" s="623">
+      <c r="E20" s="625">
         <v>0.65</v>
       </c>
-      <c r="F20" s="624" t="s">
+      <c r="F20" s="617" t="s">
         <v>373</v>
       </c>
-      <c r="G20" s="625"/>
-      <c r="H20" s="624" t="s">
+      <c r="G20" s="627"/>
+      <c r="H20" s="617" t="s">
         <v>374</v>
       </c>
       <c r="I20" s="383"/>
     </row>
     <row r="21" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="629"/>
-      <c r="B21" s="622"/>
+      <c r="A21" s="619"/>
+      <c r="B21" s="626"/>
       <c r="C21" s="560" t="s">
         <v>375</v>
       </c>
       <c r="D21" s="560">
         <v>4.09</v>
       </c>
-      <c r="E21" s="623"/>
-      <c r="F21" s="624"/>
-      <c r="G21" s="625"/>
-      <c r="H21" s="624"/>
+      <c r="E21" s="625"/>
+      <c r="F21" s="617"/>
+      <c r="G21" s="627"/>
+      <c r="H21" s="617"/>
       <c r="I21" s="383"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -35990,10 +36053,10 @@
       <c r="I23" s="382"/>
     </row>
     <row r="24" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="629" t="s">
+      <c r="A24" s="619" t="s">
         <v>344</v>
       </c>
-      <c r="B24" s="633" t="s">
+      <c r="B24" s="618" t="s">
         <v>378</v>
       </c>
       <c r="C24" s="453" t="s">
@@ -36002,35 +36065,35 @@
       <c r="D24" s="454" t="s">
         <v>380</v>
       </c>
-      <c r="E24" s="624">
+      <c r="E24" s="617">
         <v>0.65</v>
       </c>
-      <c r="F24" s="624" t="s">
+      <c r="F24" s="617" t="s">
         <v>381</v>
       </c>
       <c r="G24" s="455">
         <v>0.72</v>
       </c>
-      <c r="H24" s="624" t="s">
+      <c r="H24" s="617" t="s">
         <v>382</v>
       </c>
       <c r="I24" s="560"/>
     </row>
     <row r="25" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="634"/>
-      <c r="B25" s="633"/>
+      <c r="A25" s="620"/>
+      <c r="B25" s="618"/>
       <c r="C25" s="563" t="s">
         <v>383</v>
       </c>
       <c r="D25" s="456" t="s">
         <v>380</v>
       </c>
-      <c r="E25" s="635"/>
-      <c r="F25" s="635"/>
+      <c r="E25" s="621"/>
+      <c r="F25" s="621"/>
       <c r="G25" s="457">
         <v>0.67600000000000005</v>
       </c>
-      <c r="H25" s="635"/>
+      <c r="H25" s="621"/>
       <c r="I25" s="563"/>
     </row>
     <row r="26" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -36123,6 +36186,14 @@
     <row r="45" spans="5:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="H20:H21"/>
     <mergeCell ref="B24:B25"/>
@@ -36131,18 +36202,10 @@
     <mergeCell ref="F24:F25"/>
     <mergeCell ref="H24:H25"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="B10:B12"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="E20:E21"/>
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="G20:G21"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A27:I27"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
@@ -36184,20 +36247,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="615" t="str">
+      <c r="A1" s="599" t="str">
         <f>"Outdoor Airflow Rate - "&amp;Prototype!A2</f>
         <v>Outdoor Airflow Rate - RetailMedium</v>
       </c>
-      <c r="B1" s="615"/>
-      <c r="C1" s="615"/>
-      <c r="D1" s="615"/>
-      <c r="E1" s="615"/>
-      <c r="F1" s="615"/>
-      <c r="G1" s="615"/>
-      <c r="H1" s="615"/>
-      <c r="I1" s="615"/>
-      <c r="J1" s="615"/>
-      <c r="K1" s="615"/>
+      <c r="B1" s="599"/>
+      <c r="C1" s="599"/>
+      <c r="D1" s="599"/>
+      <c r="E1" s="599"/>
+      <c r="F1" s="599"/>
+      <c r="G1" s="599"/>
+      <c r="H1" s="599"/>
+      <c r="I1" s="599"/>
+      <c r="J1" s="599"/>
+      <c r="K1" s="599"/>
       <c r="L1" s="78"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -36845,28 +36908,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="615" t="str">
+      <c r="A1" s="599" t="str">
         <f>"Thermostat Setpoints - "&amp;Prototype!A2</f>
         <v>Thermostat Setpoints - RetailMedium</v>
       </c>
-      <c r="B1" s="615"/>
-      <c r="C1" s="615"/>
-      <c r="D1" s="615"/>
-      <c r="E1" s="615"/>
-      <c r="F1" s="615"/>
-      <c r="G1" s="615"/>
-      <c r="H1" s="615"/>
-      <c r="I1" s="615"/>
-      <c r="J1" s="615"/>
-      <c r="K1" s="615"/>
-      <c r="L1" s="615"/>
-      <c r="M1" s="615"/>
-      <c r="N1" s="615"/>
-      <c r="O1" s="615"/>
-      <c r="P1" s="615"/>
-      <c r="Q1" s="615"/>
-      <c r="R1" s="615"/>
-      <c r="S1" s="615"/>
+      <c r="B1" s="599"/>
+      <c r="C1" s="599"/>
+      <c r="D1" s="599"/>
+      <c r="E1" s="599"/>
+      <c r="F1" s="599"/>
+      <c r="G1" s="599"/>
+      <c r="H1" s="599"/>
+      <c r="I1" s="599"/>
+      <c r="J1" s="599"/>
+      <c r="K1" s="599"/>
+      <c r="L1" s="599"/>
+      <c r="M1" s="599"/>
+      <c r="N1" s="599"/>
+      <c r="O1" s="599"/>
+      <c r="P1" s="599"/>
+      <c r="Q1" s="599"/>
+      <c r="R1" s="599"/>
+      <c r="S1" s="599"/>
     </row>
     <row r="2" spans="1:19" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="184" t="s">
@@ -36928,7 +36991,7 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="636" t="s">
+      <c r="A3" s="628" t="s">
         <v>400</v>
       </c>
       <c r="B3" s="269" t="s">
@@ -36982,12 +37045,12 @@
       <c r="R3" s="269">
         <v>70</v>
       </c>
-      <c r="S3" s="636" t="s">
+      <c r="S3" s="628" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="637"/>
+      <c r="A4" s="629"/>
       <c r="B4" s="269" t="s">
         <v>403</v>
       </c>
@@ -37039,10 +37102,10 @@
       <c r="R4" s="269">
         <v>60</v>
       </c>
-      <c r="S4" s="637"/>
+      <c r="S4" s="629"/>
     </row>
     <row r="5" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="637"/>
+      <c r="A5" s="629"/>
       <c r="B5" s="269" t="s">
         <v>404</v>
       </c>
@@ -37094,10 +37157,10 @@
       <c r="R5" s="269">
         <v>75</v>
       </c>
-      <c r="S5" s="637"/>
+      <c r="S5" s="629"/>
     </row>
     <row r="6" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="638"/>
+      <c r="A6" s="630"/>
       <c r="B6" s="269" t="s">
         <v>405</v>
       </c>
@@ -37149,10 +37212,10 @@
       <c r="R6" s="269">
         <v>85</v>
       </c>
-      <c r="S6" s="638"/>
+      <c r="S6" s="630"/>
     </row>
     <row r="7" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="636" t="s">
+      <c r="A7" s="628" t="s">
         <v>406</v>
       </c>
       <c r="B7" s="555" t="s">
@@ -37206,12 +37269,12 @@
       <c r="R7" s="464">
         <v>60</v>
       </c>
-      <c r="S7" s="639" t="s">
+      <c r="S7" s="631" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="637"/>
+      <c r="A8" s="629"/>
       <c r="B8" s="555" t="s">
         <v>403</v>
       </c>
@@ -37263,10 +37326,10 @@
       <c r="R8" s="464">
         <v>60</v>
       </c>
-      <c r="S8" s="640"/>
+      <c r="S8" s="632"/>
     </row>
     <row r="9" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="637"/>
+      <c r="A9" s="629"/>
       <c r="B9" s="555" t="s">
         <v>404</v>
       </c>
@@ -37318,10 +37381,10 @@
       <c r="R9" s="464">
         <v>85</v>
       </c>
-      <c r="S9" s="640"/>
+      <c r="S9" s="632"/>
     </row>
     <row r="10" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="638"/>
+      <c r="A10" s="630"/>
       <c r="B10" s="555" t="s">
         <v>405</v>
       </c>
@@ -37373,7 +37436,7 @@
       <c r="R10" s="464">
         <v>85</v>
       </c>
-      <c r="S10" s="641"/>
+      <c r="S10" s="633"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -37421,16 +37484,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="643" t="str">
+      <c r="A1" s="635" t="str">
         <f>"Water Heater - "&amp;Prototype!A2</f>
         <v>Water Heater - RetailMedium</v>
       </c>
-      <c r="B1" s="626"/>
-      <c r="C1" s="626"/>
-      <c r="D1" s="626"/>
-      <c r="E1" s="626"/>
-      <c r="F1" s="626"/>
-      <c r="G1" s="626"/>
+      <c r="B1" s="622"/>
+      <c r="C1" s="622"/>
+      <c r="D1" s="622"/>
+      <c r="E1" s="622"/>
+      <c r="F1" s="622"/>
+      <c r="G1" s="622"/>
     </row>
     <row r="2" spans="1:9" ht="22.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="184" t="s">
@@ -37513,16 +37576,16 @@
       <c r="F5" s="291"/>
     </row>
     <row r="6" spans="1:9" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="650" t="s">
+      <c r="A6" s="642" t="s">
         <v>417</v>
       </c>
-      <c r="B6" s="615"/>
-      <c r="C6" s="615"/>
-      <c r="D6" s="615"/>
-      <c r="E6" s="615"/>
-      <c r="F6" s="615"/>
-      <c r="G6" s="615"/>
-      <c r="H6" s="615"/>
+      <c r="B6" s="599"/>
+      <c r="C6" s="599"/>
+      <c r="D6" s="599"/>
+      <c r="E6" s="599"/>
+      <c r="F6" s="599"/>
+      <c r="G6" s="599"/>
+      <c r="H6" s="599"/>
       <c r="I6" s="107"/>
     </row>
     <row r="7" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -37579,7 +37642,7 @@
         <f>F8/60</f>
         <v>0.87898581600000003</v>
       </c>
-      <c r="H8" s="651" t="s">
+      <c r="H8" s="643" t="s">
         <v>424</v>
       </c>
     </row>
@@ -37610,7 +37673,7 @@
         <f t="shared" ref="G9:G15" si="1">F9/60</f>
         <v>8.3113272000000002E-2</v>
       </c>
-      <c r="H9" s="652"/>
+      <c r="H9" s="644"/>
     </row>
     <row r="10" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="221" t="str">
@@ -37639,7 +37702,7 @@
         <f t="shared" si="1"/>
         <v>8.3113272000000002E-2</v>
       </c>
-      <c r="H10" s="652"/>
+      <c r="H10" s="644"/>
     </row>
     <row r="11" spans="1:9" s="3" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="221" t="str">
@@ -37668,7 +37731,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="652"/>
+      <c r="H11" s="644"/>
     </row>
     <row r="12" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="480" t="str">
@@ -37697,7 +37760,7 @@
         <f t="shared" si="1"/>
         <v>3.5556480000000002E-3</v>
       </c>
-      <c r="H12" s="652"/>
+      <c r="H12" s="644"/>
     </row>
     <row r="13" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="484" t="str">
@@ -37726,7 +37789,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H13" s="652"/>
+      <c r="H13" s="644"/>
     </row>
     <row r="14" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="486" t="str">
@@ -37755,7 +37818,7 @@
         <f t="shared" si="1"/>
         <v>1.000026E-2</v>
       </c>
-      <c r="H14" s="652"/>
+      <c r="H14" s="644"/>
     </row>
     <row r="15" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="488" t="str">
@@ -37784,18 +37847,18 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H15" s="653"/>
+      <c r="H15" s="645"/>
     </row>
     <row r="16" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="495" t="s">
         <v>163</v>
       </c>
-      <c r="B16" s="654" t="s">
+      <c r="B16" s="646" t="s">
         <v>425</v>
       </c>
-      <c r="C16" s="655"/>
-      <c r="D16" s="655"/>
-      <c r="E16" s="656"/>
+      <c r="C16" s="647"/>
+      <c r="D16" s="647"/>
+      <c r="E16" s="648"/>
       <c r="F16" s="496">
         <f>_xlfn.LET(
   _xlpm.g,SUMIF($B$8:$B$15,"Gas*",$F$8:$F$15),
@@ -37804,7 +37867,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="281"/>
-      <c r="H16" s="657" t="s">
+      <c r="H16" s="649" t="s">
         <v>426</v>
       </c>
     </row>
@@ -37812,12 +37875,12 @@
       <c r="A17" s="495" t="s">
         <v>427</v>
       </c>
-      <c r="B17" s="654" t="s">
+      <c r="B17" s="646" t="s">
         <v>428</v>
       </c>
-      <c r="C17" s="655"/>
-      <c r="D17" s="655"/>
-      <c r="E17" s="656"/>
+      <c r="C17" s="647"/>
+      <c r="D17" s="647"/>
+      <c r="E17" s="648"/>
       <c r="F17" s="496">
         <f>_xlfn.LET(
   _xlpm.g,SUMIF($B$8:$B$15,"Gas*",$F$8:$F$15),
@@ -37826,7 +37889,7 @@
         <v>75</v>
       </c>
       <c r="G17" s="281"/>
-      <c r="H17" s="658"/>
+      <c r="H17" s="650"/>
     </row>
     <row r="18" spans="1:13" s="276" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18"/>
@@ -37933,20 +37996,20 @@
       <c r="G24" s="285"/>
     </row>
     <row r="25" spans="1:13" s="276" customFormat="1" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="659" t="s">
+      <c r="A25" s="651" t="s">
         <v>436</v>
       </c>
-      <c r="B25" s="660"/>
-      <c r="C25" s="660"/>
-      <c r="D25" s="660"/>
-      <c r="E25" s="660"/>
-      <c r="F25" s="660"/>
-      <c r="G25" s="660"/>
-      <c r="H25" s="660"/>
-      <c r="I25" s="660"/>
-      <c r="J25" s="660"/>
-      <c r="K25" s="660"/>
-      <c r="L25" s="660"/>
+      <c r="B25" s="652"/>
+      <c r="C25" s="652"/>
+      <c r="D25" s="652"/>
+      <c r="E25" s="652"/>
+      <c r="F25" s="652"/>
+      <c r="G25" s="652"/>
+      <c r="H25" s="652"/>
+      <c r="I25" s="652"/>
+      <c r="J25" s="652"/>
+      <c r="K25" s="652"/>
+      <c r="L25" s="652"/>
     </row>
     <row r="26" spans="1:13" s="276" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="503" t="s">
@@ -37970,14 +38033,14 @@
       <c r="G26" s="503" t="s">
         <v>443</v>
       </c>
-      <c r="H26" s="644" t="s">
+      <c r="H26" s="636" t="s">
         <v>444</v>
       </c>
-      <c r="I26" s="645"/>
-      <c r="J26" s="646" t="s">
+      <c r="I26" s="637"/>
+      <c r="J26" s="638" t="s">
         <v>445</v>
       </c>
-      <c r="K26" s="646"/>
+      <c r="K26" s="638"/>
       <c r="L26" s="504" t="s">
         <v>446</v>
       </c>
@@ -38024,7 +38087,7 @@
       <c r="K27" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L27" s="647" t="s">
+      <c r="L27" s="639" t="s">
         <v>450</v>
       </c>
     </row>
@@ -38069,7 +38132,7 @@
       <c r="K28" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L28" s="648"/>
+      <c r="L28" s="640"/>
     </row>
     <row r="29" spans="1:13" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="505" t="s">
@@ -38112,7 +38175,7 @@
       <c r="K29" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L29" s="648"/>
+      <c r="L29" s="640"/>
     </row>
     <row r="30" spans="1:13" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="505" t="s">
@@ -38155,7 +38218,7 @@
       <c r="K30" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L30" s="648"/>
+      <c r="L30" s="640"/>
     </row>
     <row r="31" spans="1:13" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="505" t="s">
@@ -38198,7 +38261,7 @@
       <c r="K31" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L31" s="648"/>
+      <c r="L31" s="640"/>
     </row>
     <row r="32" spans="1:13" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="505" t="s">
@@ -38241,7 +38304,7 @@
       <c r="K32" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L32" s="648"/>
+      <c r="L32" s="640"/>
     </row>
     <row r="33" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="505" t="s">
@@ -38284,7 +38347,7 @@
       <c r="K33" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L33" s="648"/>
+      <c r="L33" s="640"/>
     </row>
     <row r="34" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="505" t="s">
@@ -38327,7 +38390,7 @@
       <c r="K34" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L34" s="648"/>
+      <c r="L34" s="640"/>
     </row>
     <row r="35" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="505" t="s">
@@ -38370,7 +38433,7 @@
       <c r="K35" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L35" s="648"/>
+      <c r="L35" s="640"/>
     </row>
     <row r="36" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="505" t="s">
@@ -38413,7 +38476,7 @@
       <c r="K36" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L36" s="648"/>
+      <c r="L36" s="640"/>
     </row>
     <row r="37" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="505" t="s">
@@ -38456,7 +38519,7 @@
       <c r="K37" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L37" s="648"/>
+      <c r="L37" s="640"/>
     </row>
     <row r="38" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="505" t="s">
@@ -38499,7 +38562,7 @@
       <c r="K38" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L38" s="648"/>
+      <c r="L38" s="640"/>
     </row>
     <row r="39" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="505" t="s">
@@ -38542,7 +38605,7 @@
       <c r="K39" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L39" s="648"/>
+      <c r="L39" s="640"/>
     </row>
     <row r="40" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="505" t="s">
@@ -38585,7 +38648,7 @@
       <c r="K40" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L40" s="648"/>
+      <c r="L40" s="640"/>
     </row>
     <row r="41" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="505" t="s">
@@ -38628,7 +38691,7 @@
       <c r="K41" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L41" s="648"/>
+      <c r="L41" s="640"/>
     </row>
     <row r="42" spans="1:12" s="276" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="505" t="s">
@@ -38671,7 +38734,7 @@
       <c r="K42" s="510" t="s">
         <v>449</v>
       </c>
-      <c r="L42" s="649"/>
+      <c r="L42" s="641"/>
     </row>
     <row r="43" spans="1:12" s="276" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C43" s="285"/>
@@ -38692,16 +38755,16 @@
       <c r="G45" s="285"/>
     </row>
     <row r="46" spans="1:12" s="276" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A46" s="642" t="s">
+      <c r="A46" s="634" t="s">
         <v>459</v>
       </c>
-      <c r="B46" s="615"/>
-      <c r="C46" s="615"/>
-      <c r="D46" s="615"/>
-      <c r="E46" s="615"/>
-      <c r="F46" s="615"/>
-      <c r="G46" s="615"/>
-      <c r="H46" s="615"/>
+      <c r="B46" s="599"/>
+      <c r="C46" s="599"/>
+      <c r="D46" s="599"/>
+      <c r="E46" s="599"/>
+      <c r="F46" s="599"/>
+      <c r="G46" s="599"/>
+      <c r="H46" s="599"/>
     </row>
     <row r="47" spans="1:12" s="277" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A47" s="511" t="s">
@@ -39427,17 +39490,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="642" t="str">
+      <c r="A1" s="634" t="str">
         <f>"Interior Lighting - "&amp;Prototype!A2</f>
         <v>Interior Lighting - RetailMedium</v>
       </c>
-      <c r="B1" s="615"/>
-      <c r="C1" s="615"/>
-      <c r="D1" s="615"/>
-      <c r="E1" s="615"/>
-      <c r="F1" s="615"/>
-      <c r="G1" s="615"/>
-      <c r="H1" s="615"/>
+      <c r="B1" s="599"/>
+      <c r="C1" s="599"/>
+      <c r="D1" s="599"/>
+      <c r="E1" s="599"/>
+      <c r="F1" s="599"/>
+      <c r="G1" s="599"/>
+      <c r="H1" s="599"/>
       <c r="I1" s="107"/>
       <c r="J1" s="107"/>
       <c r="K1" s="107"/>
@@ -39446,23 +39509,23 @@
       <c r="N1" s="107"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="661" t="s">
+      <c r="A2" s="653" t="s">
         <v>161</v>
       </c>
-      <c r="B2" s="663" t="s">
+      <c r="B2" s="655" t="s">
         <v>471</v>
       </c>
-      <c r="C2" s="663"/>
-      <c r="D2" s="663"/>
-      <c r="E2" s="663" t="s">
+      <c r="C2" s="655"/>
+      <c r="D2" s="655"/>
+      <c r="E2" s="655" t="s">
         <v>217</v>
       </c>
-      <c r="F2" s="663"/>
-      <c r="G2" s="663"/>
+      <c r="F2" s="655"/>
+      <c r="G2" s="655"/>
       <c r="H2" s="176"/>
     </row>
     <row r="3" spans="1:14" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="662"/>
+      <c r="A3" s="654"/>
       <c r="B3" s="176" t="s">
         <v>472</v>
       </c>
@@ -39496,7 +39559,7 @@
       <c r="C4" s="530">
         <v>0.1</v>
       </c>
-      <c r="D4" s="664" t="s">
+      <c r="D4" s="656" t="s">
         <v>475</v>
       </c>
       <c r="E4" s="560">
@@ -39505,7 +39568,7 @@
       <c r="F4" s="560" t="s">
         <v>476</v>
       </c>
-      <c r="G4" s="664" t="s">
+      <c r="G4" s="656" t="s">
         <v>477</v>
       </c>
       <c r="H4" s="560" t="s">
@@ -39521,12 +39584,12 @@
         <v>0.6</v>
       </c>
       <c r="C5" s="560"/>
-      <c r="D5" s="665"/>
+      <c r="D5" s="657"/>
       <c r="E5" s="560">
         <v>0.9</v>
       </c>
       <c r="F5" s="560"/>
-      <c r="G5" s="665"/>
+      <c r="G5" s="657"/>
       <c r="H5" s="560" t="s">
         <v>479</v>
       </c>
@@ -39540,12 +39603,12 @@
         <v>0.65</v>
       </c>
       <c r="C6" s="532"/>
-      <c r="D6" s="665"/>
+      <c r="D6" s="657"/>
       <c r="E6" s="533">
         <v>0.6</v>
       </c>
       <c r="F6" s="532"/>
-      <c r="G6" s="665"/>
+      <c r="G6" s="657"/>
       <c r="H6" s="532"/>
     </row>
     <row r="7" spans="1:14" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -39557,12 +39620,12 @@
         <v>0.4</v>
       </c>
       <c r="C7" s="224"/>
-      <c r="D7" s="665"/>
+      <c r="D7" s="657"/>
       <c r="E7" s="532">
         <v>0.6</v>
       </c>
       <c r="F7" s="225"/>
-      <c r="G7" s="665"/>
+      <c r="G7" s="657"/>
       <c r="H7" s="534" t="s">
         <v>480</v>
       </c>
@@ -39579,7 +39642,7 @@
         <f>0.52*0.2</f>
         <v>0.10400000000000001</v>
       </c>
-      <c r="D8" s="665"/>
+      <c r="D8" s="657"/>
       <c r="E8" s="561">
         <v>1.2</v>
       </c>
@@ -39587,7 +39650,7 @@
         <f>0.3*0.2</f>
         <v>0.06</v>
       </c>
-      <c r="G8" s="665"/>
+      <c r="G8" s="657"/>
       <c r="H8" s="560" t="s">
         <v>481</v>
       </c>
@@ -39601,12 +39664,12 @@
         <v>0.7</v>
       </c>
       <c r="C9" s="175"/>
-      <c r="D9" s="666"/>
+      <c r="D9" s="658"/>
       <c r="E9" s="560">
         <v>0.95</v>
       </c>
       <c r="F9" s="174"/>
-      <c r="G9" s="666"/>
+      <c r="G9" s="658"/>
       <c r="H9" s="532" t="s">
         <v>482</v>
       </c>
@@ -39635,6 +39698,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003D1D6A7EB2452B4A86A9506D4E13D4C9" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7cd6ed0cd056f112062446d0d1c544ce">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="41613948-0554-4f13-babe-277410c056ca" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60ca449bf2be89171a15d05d28af00ea" ns2:_="">
     <xsd:import namespace="41613948-0554-4f13-babe-277410c056ca"/>
@@ -39772,22 +39850,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20816333-575B-4274-8A3E-18699B071E90}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7921AF10-0BF8-441A-BDBA-64AF3E09D45F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEBB9FA9-CB63-4711-8EA9-B5E13AE284E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -39803,21 +39883,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7921AF10-0BF8-441A-BDBA-64AF3E09D45F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20816333-575B-4274-8A3E-18699B071E90}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>